--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Đội ngũ" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Sprint" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Rủi ro" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Nhật ký" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$4:$O$129</definedName>
@@ -30,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="894">
   <si>
     <t xml:space="preserve">GoAn — Bảng theo dõi dự án (Project Tracker)</t>
   </si>
   <si>
-    <t xml:space="preserve">Đội 4 người · 8 giai đoạn · Đánh giá hiện trạng dựa trên rà soát mã nguồn thực tế ngày 03/09/2026</t>
+    <t xml:space="preserve">Đội 4 người · 8 giai đoạn · Cập nhật lần cuối 03/09/2026 sau khi triển khai đợt P0 đầu tiên (2 commit)</t>
   </si>
   <si>
     <t xml:space="preserve">CÁC SHEET</t>
@@ -74,7 +75,13 @@
     <t xml:space="preserve">Rủi ro</t>
   </si>
   <si>
-    <t xml:space="preserve">8 rủi ro đã nhận diện, kèm cách giảm thiểu và người chịu trách nhiệm.</t>
+    <t xml:space="preserve">9 rủi ro đã nhận diện, kèm cách giảm thiểu và người chịu trách nhiệm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhật ký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Việc đã triển khai thật, kèm mã commit và bằng chứng kiểm chứng. Cả những chỗ đánh giá ban đầu sai và đã được sửa lại.</t>
   </si>
   <si>
     <t xml:space="preserve">Lists</t>
@@ -566,7 +573,7 @@
     <t xml:space="preserve">TL</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã kiểm chứng: goan-backend chỉ 9 endpoint, 1 file test, thiếu .env — bị goan-backend-spec vượt hoàn toàn</t>
+    <t xml:space="preserve">03/09: đã chuyển thành services/_deprecated-api-v0 kèm DEPRECATED.md (bảng so sánh 9 vs 33 endpoint). Chưa xoá hẳn vì apps/customer-web còn viết theo API này — xoá sau khi xong P4-12</t>
   </si>
   <si>
     <t xml:space="preserve">P0-02</t>
@@ -578,6 +585,9 @@
     <t xml:space="preserve">pnpm i chạy được ở root; turbo build/lint/test xanh</t>
   </si>
   <si>
+    <t xml:space="preserve">03/09 XONG: pnpm-workspace.yaml + turbo.json + .editorconfig + README. pnpm install xanh (244 gói), pnpm-lock.yaml đã commit, pnpm build xanh</t>
+  </si>
+  <si>
     <t xml:space="preserve">P0-03</t>
   </si>
   <si>
@@ -593,6 +603,9 @@
     <t xml:space="preserve">Dựng monorepo</t>
   </si>
   <si>
+    <t xml:space="preserve">03/09 XONG: 181 file đổi đường dẫn, 51/51 test vẫn xanh. goan-customer-app → apps/customer-web (@goan/customer-web)</t>
+  </si>
+  <si>
     <t xml:space="preserve">P0-04</t>
   </si>
   <si>
@@ -602,6 +615,9 @@
     <t xml:space="preserve">docs/ có đủ 4 tài liệu, README root trỏ tới</t>
   </si>
   <si>
+    <t xml:space="preserve">03/09 XONG: docs/ có 3 tài liệu + file tracker này. README root có bảng dẫn đường</t>
+  </si>
+  <si>
     <t xml:space="preserve">P0-05</t>
   </si>
   <si>
@@ -614,7 +630,7 @@
     <t xml:space="preserve">0 lỗi ruff, mypy pass ở mức strict cho domains/</t>
   </si>
   <si>
-    <t xml:space="preserve">pyproject.toml đã có sẵn, chưa cấu hình lint/type</t>
+    <t xml:space="preserve">03/09 XONG: ruff (E,F,I,UP,B,C4,SIM,ASYNC) sạch sau khi sửa 92 lỗi; ruff format toàn bộ; mypy SẠCH 78 file. Sửa được 3 bug tiềm ẩn thật — xem sheet Nhật ký</t>
   </si>
   <si>
     <t xml:space="preserve">P0-06</t>
@@ -629,7 +645,7 @@
     <t xml:space="preserve">Di chuyển services/api</t>
   </si>
   <si>
-    <t xml:space="preserve">Đây là biện pháp chặn tận gốc lỗi lệch endpoint FE-BE hiện tại</t>
+    <t xml:space="preserve">03/09 XONG: export_openapi.py xuất 33 đường dẫn / 54 schema; openapi-typescript sinh schema.d.ts 2.168 dòng; @goan/api-client typecheck sạch; CI có job so sánh chống lệch</t>
   </si>
   <si>
     <t xml:space="preserve">P0-07</t>
@@ -644,6 +660,9 @@
     <t xml:space="preserve">PR không merge được khi CI đỏ</t>
   </si>
   <si>
+    <t xml:space="preserve">03/09: .github/workflows/ci.yml có 4 job (backend, migration-check, api-contract, frontend), KHÔNG còn continue-on-error nào. Còn lại: push lên GitHub và chạy thật 1 lần để xác nhận</t>
+  </si>
+  <si>
     <t xml:space="preserve">P0-08</t>
   </si>
   <si>
@@ -656,6 +675,9 @@
     <t xml:space="preserve">GitHub Actions</t>
   </si>
   <si>
+    <t xml:space="preserve">03/09: job migration-check chạy alembic upgrade head + alembic check trên container postgis/postgis:16-3.4. Chưa xác nhận thật vì chưa push</t>
+  </si>
+  <si>
     <t xml:space="preserve">P0-09</t>
   </si>
   <si>
@@ -692,13 +714,13 @@
     <t xml:space="preserve">P0-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuyển rate limit sang Redis (token bucket theo user+IP+endpoint)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rate limit đúng khi chạy nhiều worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã kiểm chứng: RateLimitMiddleware hiện là in-process, sai khi scale ngang</t>
+    <t xml:space="preserve">Nâng cấp rate limit: cửa sổ trượt + hạn mức riêng theo endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không lách được ở ranh giới phút; OTP có hạn mức riêng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SỬA ĐÁNH GIÁ TRƯỚC: rate limit vốn ĐÃ dùng Redis, không phải in-process — đánh giá ban đầu sai. Vấn đề thật là cửa sổ cố định theo phút cho gửi gấp đôi hạn mức quanh ranh giới. 03/09 XONG: đổi sang ZSET cửa sổ trượt, thêm hạn mức riêng request-otp 5/5phút, verify-otp 10/5phút, tạo chuyến 20/phút, kèm header X-RateLimit-*</t>
   </si>
   <si>
     <t xml:space="preserve">P0-13</t>
@@ -737,7 +759,7 @@
     <t xml:space="preserve">Xoay vòng refresh token</t>
   </si>
   <si>
-    <t xml:space="preserve">config.py: ACCESS_TOKEN_EXPIRE_MINUTES = 60</t>
+    <t xml:space="preserve">03/09 XONG phía backend (ACCESS_TOKEN_EXPIRE_MINUTES = 15). LƯU Ý: apps/customer-web hiện gặp 401 là đăng xuất luôn — phải làm auto-refresh cùng lúc chuyển sang @goan/api-client (P4-12)</t>
   </si>
   <si>
     <t xml:space="preserve">P0-16</t>
@@ -764,7 +786,7 @@
     <t xml:space="preserve">K8s/LB dùng đúng probe</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã kiểm chứng: /health hiện kiểm cả DB+Redis, đang lẫn 2 vai trò</t>
+    <t xml:space="preserve">03/09 XONG: /health không chạm DB (tránh restart container vô ích khi DB sự cố); /ready kiểm DB+Redis và trả 503 khi chưa sẵn sàng</t>
   </si>
   <si>
     <t xml:space="preserve">P0-18</t>
@@ -2541,6 +2563,156 @@
   </si>
   <si>
     <t xml:space="preserve">Đưa dựng staging lên đầu P0, không lùi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHẬT KÝ TRIỂN KHAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chỉ ghi việc đã chạy và đã kiểm chứng được, không ghi dự định. Nhánh: chore/p0-foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hạng mục</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã làm gì</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bằng chứng kiểm chứng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cc30b41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấu trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dựng monorepo: goan-backend-spec → services/api, goan-backend → services/_deprecated-api-v0 (kèm DEPRECATED.md), goan-customer-app → apps/customer-web, tài liệu → docs/. Thêm pnpm workspace, turbo, .editorconfig, README</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203 file thay đổi; 51/51 test vẫn xanh sau khi đổi đường dẫn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scripts/export_openapi.py xuất OpenAPI; dựng packages/api-client (openapi-typescript + openapi-fetch) làm nguồn contract duy nhất cho mọi frontend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 đường dẫn, 54 schema; CI có job so bản sinh mới với openapi.json đã commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chất lượng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấu hình ruff (E,F,I,UP,B,C4,SIM,ASYNC) + mypy + Makefile; sửa 92 lỗi lint; ruff format toàn bộ services/api</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruff check sạch, ruff format --check sạch trên 87 file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bảo mật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tách /health (liveness, không chạm DB) và /ready (readiness, trả 503). Rate limit đổi sang ZSET cửa sổ trượt + hạn mức riêng cho OTP và tạo chuyến. Access token 60 → 15 phút</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đọc lại mã: cửa sổ cố định cũ cho gửi gấp đôi hạn mức OTP quanh ranh giới phút</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ea79c35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểu dữ liệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mypy sạch toàn bộ. BUG THẬT #1: complete_trip chỉ kiểm dropoff_lat mà bỏ sót dropoff_lng → haversine_m nhận None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mypy: Argument 4 to haversine_m has incompatible type float | None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG THẬT #2: ensure_utc trả datetime|None nên mọi phép trừ thời gian ở trips/fraud không an toàn kiểu → thêm overload (datetime vào thì datetime ra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mypy: No overload variant of __sub__ of datetime matches argument type None (2 chỗ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG THẬT #3: notify_users nhận list bất biến nên caller truyền list[UUID] không khớp list[UUID|str] → đổi sang Sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mypy: Argument 1 to notify_users has incompatible type list[UUID]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bỏ toàn bộ continue-on-error: mypy, pnpm install --frozen-lockfile, sinh api-client, typecheck và build đều chặn merge thật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pnpm install xanh (244 gói), pnpm build xanh, @goan/api-client typecheck sạch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ĐÁNH GIÁ BAN ĐẦU ĐÃ ĐƯỢC SỬA LẠI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghi lại để lần sau không lặp lại, và để ai đọc bảng này biết con số nào đã thay đổi vì sao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chủ đề</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã nói ban đầu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã xử lý thế nào</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đánh giá 03/09 sáng: 'RateLimitMiddleware là in-process, sai khi scale ngang'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAI. Đọc kỹ mã thì middleware vốn đã dùng Redis. Vấn đề thật nhỏ hơn nhưng vẫn đáng sửa: cửa sổ cố định theo phút cho phép gửi gấp đôi hạn mức quanh ranh giới phút — với endpoint gửi OTP thì mỗi tin là chi phí SMS thật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã sửa cả mã lẫn dòng task tương ứng trong Backlog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đường găng dự án</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giả định ban đầu: mobile là điểm nghẽn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số liệu nói khác: Backend cần ~24 sprint một mình, Mobile ~14, Frontend ~16, Tech Lead chỉ ~9. Backend mới là đường găng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã đổi rủi ro R1 và thêm R1b; xem sheet Rủi ro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Môi trường chạy test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dự kiến chạy test bằng .venv sẵn có trong repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.venv trong repo build cho macOS nên không dùng được từ môi trường Linux của cầu nối; ngoài ra máy chỉ có Python 3.10 trong khi dự án yêu cầu 3.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã tạo venv riêng ngoài repo để chạy test; giữ timezone.utc thay vì datetime.UTC (tắt luật UP017) để mã còn chạy được trên 3.10</t>
   </si>
 </sst>
 </file>
@@ -2553,7 +2725,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2664,8 +2836,22 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Courier New"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2694,6 +2880,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9C0006"/>
+        <bgColor rgb="FF800000"/>
       </patternFill>
     </fill>
   </fills>
@@ -2746,7 +2938,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2877,6 +3069,22 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3267,7 +3475,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3348,7 +3556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
@@ -3357,23 +3565,23 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="5"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
@@ -3400,23 +3608,23 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
+      <c r="B19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="5"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
         <v>28</v>
       </c>
+      <c r="C21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
@@ -3443,23 +3651,23 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
+      <c r="B25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="5"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
@@ -3486,25 +3694,25 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
+      <c r="B31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
         <v>47</v>
       </c>
@@ -3521,23 +3729,23 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
+      <c r="B36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="5"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="4" t="s">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
         <v>53</v>
       </c>
+      <c r="C38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="3" t="s">
@@ -3547,7 +3755,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="3" t="s">
         <v>56</v>
       </c>
@@ -3555,12 +3763,20 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3600,7 +3816,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3615,7 +3831,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3630,42 +3846,42 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5)</f>
@@ -3673,15 +3889,15 @@
       </c>
       <c r="C5" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Đã xong")</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Đang làm")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Bị chặn")</f>
@@ -3693,15 +3909,15 @@
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A5)</f>
-        <v>44.6</v>
+        <v>25.65</v>
       </c>
       <c r="I5" s="11" t="n">
         <f aca="false">IFERROR(1-H5/G5,1)</f>
-        <v>0.0408602150537634</v>
+        <v>0.448387096774194</v>
       </c>
       <c r="J5" s="10" t="n">
         <f aca="false">IFERROR(ROUND(H5/$B$16,1),0)</f>
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="K5" s="8" t="str">
         <f aca="false">IF(F5&gt;0,"Có việc bị chặn",IF(I5&gt;=1,"Hoàn thành",IF(D5&gt;0,"Đang chạy","Chưa bắt đầu")))</f>
@@ -3710,7 +3926,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A6)</f>
@@ -3755,7 +3971,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A7)</f>
@@ -3800,7 +4016,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A8)</f>
@@ -3845,7 +4061,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A9)</f>
@@ -3890,7 +4106,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A10)</f>
@@ -3935,7 +4151,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A11)</f>
@@ -3980,7 +4196,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A12)</f>
@@ -4025,7 +4241,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">SUM(B5:B12)</f>
@@ -4033,15 +4249,15 @@
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">SUM(C5:C12)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">SUM(D5:D12)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">SUM(E5:E12)</f>
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">SUM(F5:F12)</f>
@@ -4053,76 +4269,76 @@
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">SUM(H5:H12)</f>
-        <v>439.6</v>
+        <v>420.65</v>
       </c>
       <c r="I13" s="15" t="n">
         <f aca="false">IFERROR(1-H13/G13,0)</f>
-        <v>0.00430351075877689</v>
+        <v>0.0472253680634203</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">IFERROR(ROUND(H13/$B$16,1),0)</f>
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="K13" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">'Đội ngũ'!F9</f>
         <v>27.2</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" s="19" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" s="20" t="n">
         <f aca="false">ROUND(H13/B16,1)</f>
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B21" s="20" t="n">
         <f aca="false">ROUND(B20*B17,0)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4139,7 +4355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E83049BA-8972-427D-91BE-67A8731E27BC}</x14:id>
+          <x14:id>{2CEBB846-36B4-4FEC-846A-80D84746E2C5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4160,7 +4376,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E83049BA-8972-427D-91BE-67A8731E27BC}">
+          <x14:cfRule type="dataBar" id="{2CEBB846-36B4-4FEC-846A-80D84746E2C5}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4196,7 +4412,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4205,7 +4421,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4214,393 +4430,393 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" s="23" t="n">
         <v>0.9</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>0.85</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>0.95</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>0.95</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>0.45</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>0.55</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>0.5</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>0.6</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>129</v>
-      </c>
       <c r="E16" s="21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>0.5</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>0.15</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>0.4</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -4617,7 +4833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8BD08A76-83C0-4EAD-B6FF-1A56552AD8F6}</x14:id>
+          <x14:id>{6B432EDF-95A0-4095-872F-38F1D838D6F8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4644,7 +4860,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8BD08A76-83C0-4EAD-B6FF-1A56552AD8F6}">
+          <x14:cfRule type="dataBar" id="{6B432EDF-95A0-4095-872F-38F1D838D6F8}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4690,7 +4906,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4709,7 +4925,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4728,416 +4944,426 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="24" t="s">
         <v>31</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M5" s="25" t="n">
         <f aca="false">H5*(1-L5)</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N5" s="24"/>
       <c r="O5" s="21" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>179</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>177</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="25" t="n">
         <f aca="false">H6*(1-L6)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" s="24"/>
-      <c r="O6" s="21"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O6" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="25" t="n">
         <f aca="false">H7*(1-L7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="24"/>
-      <c r="O7" s="21"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O7" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L8" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="25" t="n">
         <f aca="false">H8*(1-L8)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N8" s="24"/>
-      <c r="O8" s="21"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O8" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J9" s="21"/>
       <c r="K9" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L9" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="25" t="n">
         <f aca="false">H9*(1-L9)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="24"/>
       <c r="O9" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L10" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="25" t="n">
         <f aca="false">H10*(1-L10)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" s="24"/>
       <c r="O10" s="21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>31</v>
       </c>
       <c r="L11" s="26" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M11" s="25" t="n">
         <f aca="false">H11*(1-L11)</f>
-        <v>3</v>
+        <v>0.45</v>
       </c>
       <c r="N11" s="24"/>
-      <c r="O11" s="21"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O11" s="21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>31</v>
       </c>
       <c r="L12" s="26" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M12" s="25" t="n">
         <f aca="false">H12*(1-L12)</f>
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="N12" s="24"/>
-      <c r="O12" s="21"/>
+      <c r="O12" s="21" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L13" s="26" t="n">
         <v>0.7</v>
@@ -5148,40 +5374,40 @@
       </c>
       <c r="N13" s="24"/>
       <c r="O13" s="21" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L14" s="26" t="n">
         <v>0</v>
@@ -5195,33 +5421,33 @@
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L15" s="26" t="n">
         <v>0</v>
@@ -5232,80 +5458,80 @@
       </c>
       <c r="N15" s="24"/>
       <c r="O15" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L16" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="25" t="n">
         <f aca="false">H16*(1-L16)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="24"/>
       <c r="O16" s="21" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L17" s="26" t="n">
         <v>0</v>
@@ -5316,38 +5542,38 @@
       </c>
       <c r="N17" s="24"/>
       <c r="O17" s="21" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L18" s="26" t="n">
         <v>0</v>
@@ -5358,84 +5584,84 @@
       </c>
       <c r="N18" s="24"/>
       <c r="O18" s="21" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L19" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="25" t="n">
         <f aca="false">H19*(1-L19)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="24"/>
       <c r="O19" s="21" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J20" s="21" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L20" s="26" t="n">
         <v>0</v>
@@ -5446,82 +5672,82 @@
       </c>
       <c r="N20" s="24"/>
       <c r="O20" s="21" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="24" t="s">
         <v>29</v>
       </c>
       <c r="L21" s="26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M21" s="25" t="n">
         <f aca="false">H21*(1-L21)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N21" s="24"/>
       <c r="O21" s="21" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L22" s="26" t="n">
         <v>0</v>
@@ -5532,38 +5758,38 @@
       </c>
       <c r="N22" s="24"/>
       <c r="O22" s="21" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L23" s="26" t="n">
         <v>0</v>
@@ -5577,33 +5803,33 @@
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L24" s="26" t="n">
         <v>1</v>
@@ -5614,38 +5840,38 @@
       </c>
       <c r="N24" s="24"/>
       <c r="O24" s="21" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L25" s="26" t="n">
         <v>1</v>
@@ -5656,38 +5882,38 @@
       </c>
       <c r="N25" s="24"/>
       <c r="O25" s="21" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L26" s="26" t="n">
         <v>1</v>
@@ -5698,40 +5924,40 @@
       </c>
       <c r="N26" s="24"/>
       <c r="O26" s="21" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K27" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L27" s="26" t="n">
         <v>0</v>
@@ -5742,40 +5968,40 @@
       </c>
       <c r="N27" s="24"/>
       <c r="O27" s="21" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K28" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L28" s="26" t="n">
         <v>0</v>
@@ -5789,35 +6015,35 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="24" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F29" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J29" s="21" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K29" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L29" s="26" t="n">
         <v>0</v>
@@ -5831,35 +6057,35 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J30" s="21" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K30" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L30" s="26" t="n">
         <v>0</v>
@@ -5873,35 +6099,35 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="24" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J31" s="21" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="K31" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L31" s="26" t="n">
         <v>0</v>
@@ -5915,35 +6141,35 @@
     </row>
     <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J32" s="21" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L32" s="26" t="n">
         <v>0</v>
@@ -5954,40 +6180,40 @@
       </c>
       <c r="N32" s="24"/>
       <c r="O32" s="21" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="24" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G33" s="21"/>
       <c r="H33" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J33" s="21" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K33" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L33" s="26" t="n">
         <v>0</v>
@@ -6001,35 +6227,35 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G34" s="21"/>
       <c r="H34" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J34" s="21" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L34" s="26" t="n">
         <v>0</v>
@@ -6040,40 +6266,40 @@
       </c>
       <c r="N34" s="24"/>
       <c r="O34" s="21" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="24" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G35" s="21"/>
       <c r="H35" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J35" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K35" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L35" s="26" t="n">
         <v>0</v>
@@ -6084,40 +6310,40 @@
       </c>
       <c r="N35" s="24"/>
       <c r="O35" s="21" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="24" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G36" s="21"/>
       <c r="H36" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J36" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K36" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L36" s="26" t="n">
         <v>0</v>
@@ -6131,35 +6357,35 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="24" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G37" s="21"/>
       <c r="H37" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K37" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L37" s="26" t="n">
         <v>0</v>
@@ -6170,40 +6396,40 @@
       </c>
       <c r="N37" s="24"/>
       <c r="O37" s="21" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G38" s="21"/>
       <c r="H38" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J38" s="21" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K38" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L38" s="26" t="n">
         <v>0</v>
@@ -6217,35 +6443,35 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G39" s="21"/>
       <c r="H39" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K39" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L39" s="26" t="n">
         <v>0</v>
@@ -6259,35 +6485,35 @@
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E40" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F40" s="24" t="s">
         <v>318</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>311</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J40" s="21" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K40" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L40" s="26" t="n">
         <v>0</v>
@@ -6301,35 +6527,35 @@
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="24" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G41" s="21"/>
       <c r="H41" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K41" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L41" s="26" t="n">
         <v>0</v>
@@ -6343,35 +6569,35 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="24" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J42" s="21" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="K42" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L42" s="26" t="n">
         <v>0</v>
@@ -6385,35 +6611,35 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="24" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G43" s="21"/>
       <c r="H43" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="K43" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L43" s="26" t="n">
         <v>0</v>
@@ -6427,35 +6653,35 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="24" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G44" s="21"/>
       <c r="H44" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J44" s="21" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="K44" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L44" s="26" t="n">
         <v>0</v>
@@ -6469,35 +6695,35 @@
     </row>
     <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="24" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G45" s="21"/>
       <c r="H45" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J45" s="21" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="K45" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L45" s="26" t="n">
         <v>0</v>
@@ -6511,35 +6737,35 @@
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="24" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G46" s="21"/>
       <c r="H46" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J46" s="21" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K46" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L46" s="26" t="n">
         <v>0</v>
@@ -6550,40 +6776,40 @@
       </c>
       <c r="N46" s="24"/>
       <c r="O46" s="21" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="24" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G47" s="21"/>
       <c r="H47" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J47" s="21" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K47" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L47" s="26" t="n">
         <v>0</v>
@@ -6597,35 +6823,35 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="24" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G48" s="21"/>
       <c r="H48" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K48" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L48" s="26" t="n">
         <v>0</v>
@@ -6639,35 +6865,35 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="24" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G49" s="21"/>
       <c r="H49" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K49" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L49" s="26" t="n">
         <v>0</v>
@@ -6681,35 +6907,35 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="24" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G50" s="21"/>
       <c r="H50" s="25" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J50" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K50" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L50" s="26" t="n">
         <v>0</v>
@@ -6723,35 +6949,35 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="24" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G51" s="21"/>
       <c r="H51" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K51" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L51" s="26" t="n">
         <v>0</v>
@@ -6762,40 +6988,40 @@
       </c>
       <c r="N51" s="24"/>
       <c r="O51" s="21" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G52" s="21"/>
       <c r="H52" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J52" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K52" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L52" s="26" t="n">
         <v>0</v>
@@ -6809,35 +7035,35 @@
     </row>
     <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="24" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G53" s="21"/>
       <c r="H53" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K53" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L53" s="26" t="n">
         <v>0</v>
@@ -6851,35 +7077,35 @@
     </row>
     <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="24" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G54" s="21"/>
       <c r="H54" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J54" s="21" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K54" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L54" s="26" t="n">
         <v>0</v>
@@ -6893,35 +7119,35 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="24" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G55" s="21"/>
       <c r="H55" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J55" s="21" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K55" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L55" s="26" t="n">
         <v>0</v>
@@ -6935,35 +7161,35 @@
     </row>
     <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G56" s="21"/>
       <c r="H56" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J56" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K56" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L56" s="26" t="n">
         <v>0</v>
@@ -6974,40 +7200,40 @@
       </c>
       <c r="N56" s="24"/>
       <c r="O56" s="21" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="24" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G57" s="21"/>
       <c r="H57" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J57" s="21" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K57" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L57" s="26" t="n">
         <v>0</v>
@@ -7021,35 +7247,35 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="24" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G58" s="21"/>
       <c r="H58" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K58" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L58" s="26" t="n">
         <v>0</v>
@@ -7060,40 +7286,40 @@
       </c>
       <c r="N58" s="24"/>
       <c r="O58" s="21" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="24" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G59" s="21"/>
       <c r="H59" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K59" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L59" s="26" t="n">
         <v>0</v>
@@ -7104,40 +7330,40 @@
       </c>
       <c r="N59" s="24"/>
       <c r="O59" s="21" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="24" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G60" s="21"/>
       <c r="H60" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J60" s="21" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="K60" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L60" s="26" t="n">
         <v>0</v>
@@ -7151,35 +7377,35 @@
     </row>
     <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="24" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G61" s="21"/>
       <c r="H61" s="25" t="n">
         <v>8</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K61" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L61" s="26" t="n">
         <v>0</v>
@@ -7193,35 +7419,35 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="24" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G62" s="21"/>
       <c r="H62" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="K62" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L62" s="26" t="n">
         <v>0</v>
@@ -7235,35 +7461,35 @@
     </row>
     <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G63" s="21"/>
       <c r="H63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J63" s="21" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="K63" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L63" s="26" t="n">
         <v>0</v>
@@ -7277,35 +7503,35 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="24" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G64" s="21"/>
       <c r="H64" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J64" s="21" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K64" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L64" s="26" t="n">
         <v>0</v>
@@ -7319,35 +7545,35 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G65" s="21"/>
       <c r="H65" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J65" s="21" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K65" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L65" s="26" t="n">
         <v>0</v>
@@ -7361,35 +7587,35 @@
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="24" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G66" s="21"/>
       <c r="H66" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="K66" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L66" s="26" t="n">
         <v>0</v>
@@ -7403,35 +7629,35 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="24" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G67" s="21"/>
       <c r="H67" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J67" s="21" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="K67" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L67" s="26" t="n">
         <v>0</v>
@@ -7442,40 +7668,40 @@
       </c>
       <c r="N67" s="24"/>
       <c r="O67" s="21" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="24" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G68" s="21"/>
       <c r="H68" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="K68" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L68" s="26" t="n">
         <v>0</v>
@@ -7489,35 +7715,35 @@
     </row>
     <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="F69" s="24" t="s">
         <v>426</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>428</v>
-      </c>
-      <c r="F69" s="24" t="s">
-        <v>419</v>
       </c>
       <c r="G69" s="21"/>
       <c r="H69" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J69" s="21" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="K69" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L69" s="26" t="n">
         <v>0</v>
@@ -7531,33 +7757,33 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="24" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G70" s="21"/>
       <c r="H70" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J70" s="21"/>
       <c r="K70" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L70" s="26" t="n">
         <v>0</v>
@@ -7568,40 +7794,40 @@
       </c>
       <c r="N70" s="24"/>
       <c r="O70" s="21" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="24" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G71" s="21"/>
       <c r="H71" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J71" s="21" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K71" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L71" s="26" t="n">
         <v>0</v>
@@ -7612,40 +7838,40 @@
       </c>
       <c r="N71" s="24"/>
       <c r="O71" s="21" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="24" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G72" s="21"/>
       <c r="H72" s="25" t="n">
         <v>8</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J72" s="21" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="K72" s="24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L72" s="26" t="n">
         <v>0</v>
@@ -7656,40 +7882,40 @@
       </c>
       <c r="N72" s="24"/>
       <c r="O72" s="21" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="E73" s="21" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G73" s="21"/>
       <c r="H73" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J73" s="21" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="K73" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L73" s="26" t="n">
         <v>0</v>
@@ -7700,40 +7926,40 @@
       </c>
       <c r="N73" s="24"/>
       <c r="O73" s="21" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G74" s="21"/>
       <c r="H74" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J74" s="21" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="K74" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L74" s="26" t="n">
         <v>0</v>
@@ -7747,35 +7973,35 @@
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G75" s="21"/>
       <c r="H75" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I75" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J75" s="21" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="K75" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L75" s="26" t="n">
         <v>0</v>
@@ -7786,40 +8012,40 @@
       </c>
       <c r="N75" s="24"/>
       <c r="O75" s="21" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G76" s="21"/>
       <c r="H76" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I76" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="K76" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L76" s="26" t="n">
         <v>0</v>
@@ -7830,40 +8056,40 @@
       </c>
       <c r="N76" s="24"/>
       <c r="O76" s="21" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G77" s="21"/>
       <c r="H77" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J77" s="21" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="K77" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L77" s="26" t="n">
         <v>0</v>
@@ -7877,35 +8103,35 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G78" s="21"/>
       <c r="H78" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I78" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J78" s="21" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K78" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L78" s="26" t="n">
         <v>0</v>
@@ -7919,35 +8145,35 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="24" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G79" s="21"/>
       <c r="H79" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J79" s="21" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="K79" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L79" s="26" t="n">
         <v>0</v>
@@ -7961,35 +8187,35 @@
     </row>
     <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="24" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G80" s="21"/>
       <c r="H80" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I80" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J80" s="21" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K80" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L80" s="26" t="n">
         <v>0</v>
@@ -8003,35 +8229,35 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="24" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E81" s="21" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G81" s="21"/>
       <c r="H81" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I81" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J81" s="21" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="K81" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L81" s="26" t="n">
         <v>0</v>
@@ -8045,35 +8271,35 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="24" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G82" s="21"/>
       <c r="H82" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I82" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J82" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K82" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L82" s="26" t="n">
         <v>0</v>
@@ -8087,35 +8313,35 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="24" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E83" s="21" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G83" s="21"/>
       <c r="H83" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I83" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="K83" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L83" s="26" t="n">
         <v>0</v>
@@ -8129,35 +8355,35 @@
     </row>
     <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="24" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G84" s="21"/>
       <c r="H84" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="K84" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L84" s="26" t="n">
         <v>0</v>
@@ -8171,35 +8397,35 @@
     </row>
     <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="24" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="E85" s="21" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G85" s="21"/>
       <c r="H85" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I85" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="K85" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L85" s="26" t="n">
         <v>0</v>
@@ -8213,35 +8439,35 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="24" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G86" s="21"/>
       <c r="H86" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="K86" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L86" s="26" t="n">
         <v>0</v>
@@ -8255,35 +8481,35 @@
     </row>
     <row r="87" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="24" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G87" s="21"/>
       <c r="H87" s="25" t="n">
         <v>6</v>
       </c>
       <c r="I87" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J87" s="21" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="K87" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L87" s="26" t="n">
         <v>0</v>
@@ -8294,40 +8520,40 @@
       </c>
       <c r="N87" s="24"/>
       <c r="O87" s="21" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="24" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G88" s="21"/>
       <c r="H88" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="K88" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L88" s="26" t="n">
         <v>0</v>
@@ -8341,35 +8567,35 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="24" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G89" s="21"/>
       <c r="H89" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I89" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J89" s="21" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="K89" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L89" s="26" t="n">
         <v>0</v>
@@ -8380,40 +8606,40 @@
       </c>
       <c r="N89" s="24"/>
       <c r="O89" s="21" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="24" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G90" s="21"/>
       <c r="H90" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I90" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J90" s="21" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="K90" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L90" s="26" t="n">
         <v>0</v>
@@ -8427,35 +8653,35 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="24" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G91" s="21"/>
       <c r="H91" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I91" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J91" s="21" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="K91" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L91" s="26" t="n">
         <v>0</v>
@@ -8469,35 +8695,35 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="24" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="F92" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G92" s="21"/>
       <c r="H92" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J92" s="21" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="K92" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L92" s="26" t="n">
         <v>0</v>
@@ -8511,35 +8737,35 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="24" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="E93" s="21" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G93" s="21"/>
       <c r="H93" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I93" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J93" s="21" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="K93" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L93" s="26" t="n">
         <v>0</v>
@@ -8553,35 +8779,35 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="24" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G94" s="21"/>
       <c r="H94" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I94" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J94" s="21" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="K94" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L94" s="26" t="n">
         <v>0</v>
@@ -8592,40 +8818,40 @@
       </c>
       <c r="N94" s="24"/>
       <c r="O94" s="21" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="24" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="E95" s="21" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G95" s="21"/>
       <c r="H95" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I95" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J95" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K95" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L95" s="26" t="n">
         <v>0</v>
@@ -8636,40 +8862,40 @@
       </c>
       <c r="N95" s="24"/>
       <c r="O95" s="21" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="24" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G96" s="21"/>
       <c r="H96" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J96" s="21" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="K96" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L96" s="26" t="n">
         <v>0</v>
@@ -8680,40 +8906,40 @@
       </c>
       <c r="N96" s="24"/>
       <c r="O96" s="21" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="24" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="E97" s="21" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G97" s="21"/>
       <c r="H97" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I97" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J97" s="21" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="K97" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L97" s="26" t="n">
         <v>0</v>
@@ -8727,35 +8953,35 @@
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="24" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G98" s="21"/>
       <c r="H98" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J98" s="21" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="K98" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L98" s="26" t="n">
         <v>0</v>
@@ -8766,40 +8992,40 @@
       </c>
       <c r="N98" s="24"/>
       <c r="O98" s="21" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="24" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="E99" s="21" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G99" s="21"/>
       <c r="H99" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I99" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J99" s="21" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K99" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L99" s="26" t="n">
         <v>0</v>
@@ -8813,35 +9039,35 @@
     </row>
     <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="24" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G100" s="21"/>
       <c r="H100" s="25" t="n">
         <v>6</v>
       </c>
       <c r="I100" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J100" s="21" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K100" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L100" s="26" t="n">
         <v>0</v>
@@ -8855,35 +9081,35 @@
     </row>
     <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="24" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="E101" s="21" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G101" s="21"/>
       <c r="H101" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I101" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J101" s="21" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="K101" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L101" s="26" t="n">
         <v>0</v>
@@ -8894,40 +9120,40 @@
       </c>
       <c r="N101" s="24"/>
       <c r="O101" s="21" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="24" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G102" s="21"/>
       <c r="H102" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I102" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J102" s="21" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="K102" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L102" s="26" t="n">
         <v>0</v>
@@ -8938,40 +9164,40 @@
       </c>
       <c r="N102" s="24"/>
       <c r="O102" s="21" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="24" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="E103" s="21" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G103" s="21"/>
       <c r="H103" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I103" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J103" s="21" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="K103" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L103" s="26" t="n">
         <v>0</v>
@@ -8982,38 +9208,38 @@
       </c>
       <c r="N103" s="24"/>
       <c r="O103" s="21" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="24" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G104" s="21"/>
       <c r="H104" s="25" t="n">
         <v>1</v>
       </c>
       <c r="I104" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J104" s="21"/>
       <c r="K104" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L104" s="26" t="n">
         <v>0</v>
@@ -9024,40 +9250,40 @@
       </c>
       <c r="N104" s="24"/>
       <c r="O104" s="21" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="24" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="E105" s="21" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G105" s="21"/>
       <c r="H105" s="25" t="n">
         <v>6</v>
       </c>
       <c r="I105" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J105" s="21" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="K105" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L105" s="26" t="n">
         <v>0</v>
@@ -9068,40 +9294,40 @@
       </c>
       <c r="N105" s="24"/>
       <c r="O105" s="21" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="24" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E106" s="21" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G106" s="21"/>
       <c r="H106" s="25" t="n">
         <v>8</v>
       </c>
       <c r="I106" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J106" s="21" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="K106" s="24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L106" s="26" t="n">
         <v>0</v>
@@ -9112,40 +9338,40 @@
       </c>
       <c r="N106" s="24"/>
       <c r="O106" s="21" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="24" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G107" s="21"/>
       <c r="H107" s="25" t="n">
         <v>6</v>
       </c>
       <c r="I107" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J107" s="21" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K107" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L107" s="26" t="n">
         <v>0</v>
@@ -9156,40 +9382,40 @@
       </c>
       <c r="N107" s="24"/>
       <c r="O107" s="21" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="24" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G108" s="21"/>
       <c r="H108" s="25" t="n">
         <v>6</v>
       </c>
       <c r="I108" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K108" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L108" s="26" t="n">
         <v>0</v>
@@ -9203,35 +9429,35 @@
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="24" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="E109" s="21" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G109" s="21"/>
       <c r="H109" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I109" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="K109" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L109" s="26" t="n">
         <v>0</v>
@@ -9245,35 +9471,35 @@
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="24" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="E110" s="21" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G110" s="21"/>
       <c r="H110" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I110" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J110" s="21" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="K110" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L110" s="26" t="n">
         <v>0</v>
@@ -9287,35 +9513,35 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="24" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="E111" s="21" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="F111" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G111" s="21"/>
       <c r="H111" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I111" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J111" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K111" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L111" s="26" t="n">
         <v>0</v>
@@ -9326,40 +9552,40 @@
       </c>
       <c r="N111" s="24"/>
       <c r="O111" s="21" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="24" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="E112" s="21" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G112" s="21"/>
       <c r="H112" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I112" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J112" s="21" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="K112" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L112" s="26" t="n">
         <v>0</v>
@@ -9373,35 +9599,35 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="24" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="E113" s="21" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G113" s="21"/>
       <c r="H113" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I113" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J113" s="21" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="K113" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L113" s="26" t="n">
         <v>0</v>
@@ -9415,35 +9641,35 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="24" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="E114" s="21" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G114" s="21"/>
       <c r="H114" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I114" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="K114" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L114" s="26" t="n">
         <v>0</v>
@@ -9457,35 +9683,35 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="24" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="E115" s="21" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G115" s="21"/>
       <c r="H115" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I115" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J115" s="21" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="K115" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L115" s="26" t="n">
         <v>0</v>
@@ -9499,35 +9725,35 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="24" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="E116" s="21" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G116" s="21"/>
       <c r="H116" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I116" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="K116" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L116" s="26" t="n">
         <v>0</v>
@@ -9541,35 +9767,35 @@
     </row>
     <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="24" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D117" s="21" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="E117" s="21" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G117" s="21"/>
       <c r="H117" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I117" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J117" s="21" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K117" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L117" s="26" t="n">
         <v>0</v>
@@ -9583,35 +9809,35 @@
     </row>
     <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="24" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="E118" s="21" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G118" s="21"/>
       <c r="H118" s="25" t="n">
         <v>8</v>
       </c>
       <c r="I118" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J118" s="21" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="K118" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L118" s="26" t="n">
         <v>0</v>
@@ -9625,35 +9851,35 @@
     </row>
     <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="24" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="E119" s="21" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G119" s="21"/>
       <c r="H119" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I119" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J119" s="21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K119" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L119" s="26" t="n">
         <v>0</v>
@@ -9667,35 +9893,35 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="24" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="E120" s="21" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G120" s="21"/>
       <c r="H120" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I120" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J120" s="21" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="K120" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L120" s="26" t="n">
         <v>0</v>
@@ -9709,35 +9935,35 @@
     </row>
     <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="24" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="E121" s="21" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G121" s="21"/>
       <c r="H121" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I121" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J121" s="21" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="K121" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L121" s="26" t="n">
         <v>0</v>
@@ -9748,40 +9974,40 @@
       </c>
       <c r="N121" s="24"/>
       <c r="O121" s="21" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="24" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="E122" s="21" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G122" s="21"/>
       <c r="H122" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I122" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J122" s="21" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="K122" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L122" s="26" t="n">
         <v>0</v>
@@ -9795,35 +10021,35 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="24" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="E123" s="21" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G123" s="21"/>
       <c r="H123" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I123" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J123" s="21" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="K123" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L123" s="26" t="n">
         <v>0</v>
@@ -9837,35 +10063,35 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="24" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="E124" s="21" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G124" s="21"/>
       <c r="H124" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I124" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J124" s="21" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="K124" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L124" s="26" t="n">
         <v>0</v>
@@ -9879,35 +10105,35 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="24" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="E125" s="21" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G125" s="21"/>
       <c r="H125" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I125" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J125" s="21" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K125" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L125" s="26" t="n">
         <v>0</v>
@@ -9921,33 +10147,33 @@
     </row>
     <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="24" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="E126" s="21" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G126" s="21"/>
       <c r="H126" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I126" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J126" s="21"/>
       <c r="K126" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L126" s="26" t="n">
         <v>0</v>
@@ -9958,40 +10184,40 @@
       </c>
       <c r="N126" s="24"/>
       <c r="O126" s="21" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="24" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="E127" s="21" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G127" s="21"/>
       <c r="H127" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I127" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J127" s="21" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="K127" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L127" s="26" t="n">
         <v>0</v>
@@ -10005,35 +10231,35 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="24" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E128" s="21" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="F128" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G128" s="21"/>
       <c r="H128" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I128" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J128" s="21" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="K128" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L128" s="26" t="n">
         <v>0</v>
@@ -10047,35 +10273,35 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="24" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="E129" s="21" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G129" s="21"/>
       <c r="H129" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I129" s="24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J129" s="21" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="K129" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L129" s="26" t="n">
         <v>0</v>
@@ -10089,7 +10315,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="16" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="H131" s="27" t="n">
         <f aca="false">SUM(H5:H129)</f>
@@ -10097,7 +10323,7 @@
       </c>
       <c r="M131" s="27" t="n">
         <f aca="false">SUM(M5:M129)</f>
-        <v>439.6</v>
+        <v>420.65</v>
       </c>
     </row>
   </sheetData>
@@ -10129,7 +10355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FF99247E-D157-4A44-8598-5494BE74B044}</x14:id>
+          <x14:id>{E6ABD13B-60D3-45A0-B1B3-5DA3F8417C30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10161,7 +10387,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FF99247E-D157-4A44-8598-5494BE74B044}">
+          <x14:cfRule type="dataBar" id="{E6ABD13B-60D3-45A0-B1B3-5DA3F8417C30}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10196,92 +10422,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>169</v>
-      </c>
       <c r="C1" s="28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -10316,7 +10542,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10329,7 +10555,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10342,42 +10568,42 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>8</v>
@@ -10391,25 +10617,25 @@
       </c>
       <c r="G5" s="10" t="n">
         <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$F$5:$F$129,$A5)</f>
-        <v>48.1</v>
+        <v>41.35</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">IFERROR(ROUND(G5/F5,1),0)</f>
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>8</v>
@@ -10423,23 +10649,23 @@
       </c>
       <c r="G6" s="10" t="n">
         <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$F$5:$F$129,$A6)</f>
-        <v>173.5</v>
+        <v>161.3</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IFERROR(ROUND(G6/F6,1),0)</f>
-        <v>24.1</v>
+        <v>22.4</v>
       </c>
       <c r="I6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>8</v>
@@ -10460,18 +10686,18 @@
         <v>14.4</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>8</v>
@@ -10492,13 +10718,13 @@
         <v>15.8</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="13"/>
@@ -10509,19 +10735,19 @@
       </c>
       <c r="G9" s="14" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>439.6</v>
+        <v>420.65</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
@@ -10534,7 +10760,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -10547,7 +10773,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -10560,7 +10786,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -10573,7 +10799,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -10625,7 +10851,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10634,7 +10860,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10646,391 +10872,391 @@
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="E5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="E8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="B10" s="30" t="s">
+        <v>722</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>715</v>
       </c>
-      <c r="C10" s="30" t="s">
-        <v>708</v>
-      </c>
       <c r="D10" s="31" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="E15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>731</v>
-      </c>
       <c r="D16" s="8" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="E16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="E18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="E19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="E22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="E24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="30" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="E26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="30" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -11039,7 +11265,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -11048,7 +11274,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="B33" s="29"/>
       <c r="C33" s="29"/>
@@ -11057,7 +11283,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
@@ -11066,7 +11292,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
@@ -11075,7 +11301,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
@@ -11121,7 +11347,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11132,7 +11358,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11143,232 +11369,232 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
+        <v>836</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>837</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>829</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>830</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>822</v>
-      </c>
       <c r="D12" s="22" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -11397,4 +11623,271 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>852</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>853</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>854</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>852</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>856</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>857</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>852</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>859</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>860</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>852</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>862</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>863</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>865</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>866</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>867</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>865</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>866</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>869</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>865</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>866</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>871</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="s">
+        <v>851</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>865</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>873</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36" t="s">
+        <v>878</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>879</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>880</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>882</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>883</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>884</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>886</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>887</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>888</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>890</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>891</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>892</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>893</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Nhật ký" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$4:$O$129</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$4:$O$135</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="940">
   <si>
     <t xml:space="preserve">GoAn — Bảng theo dõi dự án (Project Tracker)</t>
   </si>
   <si>
-    <t xml:space="preserve">Đội 4 người · 8 giai đoạn · Cập nhật lần cuối 03/09/2026 sau khi triển khai đợt P0 đầu tiên (2 commit)</t>
+    <t xml:space="preserve">Đội 4 người · 8 giai đoạn · Cập nhật lần cuối 03/09/2026 · nhánh chore/p0-foundation, 5 commit, 129 test xanh</t>
   </si>
   <si>
     <t xml:space="preserve">CÁC SHEET</t>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Nhật ký</t>
   </si>
   <si>
-    <t xml:space="preserve">Việc đã triển khai thật, kèm mã commit và bằng chứng kiểm chứng. Cả những chỗ đánh giá ban đầu sai và đã được sửa lại.</t>
+    <t xml:space="preserve">15 việc đã triển khai thật, kèm mã commit và bằng chứng kiểm chứng. Cả những chỗ đánh giá ban đầu sai và đã được sửa lại.</t>
   </si>
   <si>
     <t xml:space="preserve">Lists</t>
@@ -732,7 +732,7 @@
     <t xml:space="preserve">Gửi trùng request không tạo 2 bản ghi; lưu Redis 24h</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có idempotency riêng lẻ ở tạo chuyến + complete, chưa có cơ chế chung</t>
+    <t xml:space="preserve">03/09 XONG: core/idempotency.py bảo vệ 5 nhóm endpoint (tạo chuyến, complete, cancel, withdraw, accept). Gửi trùng phát lại response cũ; bản gốc đang chạy trả 409. Chỉ cache kết quả thành công. 16 test QA-IDM</t>
   </si>
   <si>
     <t xml:space="preserve">P0-14</t>
@@ -744,7 +744,7 @@
     <t xml:space="preserve">Dùng lại refresh cũ → thu hồi cả họ token</t>
   </si>
   <si>
-    <t xml:space="preserve">Hiện chưa có rotation; refresh 30 ngày là rủi ro nếu lộ</t>
+    <t xml:space="preserve">03/09 XONG: theo OAuth 2.0 BCP §4.13. Mỗi lần đăng nhập = 1 họ token; dùng lại token đã tiêu thì thu hồi cả họ. Token cũ chưa có fam được nâng cấp 1 lần nên deploy không đá hết người dùng. Thêm POST /auth/logout. 9 test QA-AUTH</t>
   </si>
   <si>
     <t xml:space="preserve">P0-15</t>
@@ -774,7 +774,7 @@
     <t xml:space="preserve">Dựng staging</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có JSON logging, chưa có trace/metrics</t>
+    <t xml:space="preserve">03/09: xong X-Request-ID xuyên log/audit/response header + hook Sentry bật theo DSN (không gửi PII). CÒN LẠI: OpenTelemetry trace và Prometheus metrics, cần staging mới kiểm chứng được</t>
   </si>
   <si>
     <t xml:space="preserve">P0-17</t>
@@ -810,9 +810,96 @@
     <t xml:space="preserve">Mọi POST/PATCH/DELETE để lại: ai, IP, payload trước/sau</t>
   </si>
   <si>
+    <t xml:space="preserve">03/09 XONG: migration 0002 + domains/audit + middleware. Che đệ quy 17 trường nhạy cảm, suy ra resource_type/resource_id từ đường dẫn. Lỗi ghi audit không làm hỏng request. 19 test QA-AUD</t>
+  </si>
+  <si>
     <t xml:space="preserve">P0-20</t>
   </si>
   <si>
+    <t xml:space="preserve">QA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dựng vai trò QA: quyền hạn, quy trình, Definition of Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có tài liệu đội đọc là làm theo được, không cần hỏi lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 XONG: docs/QA/QA_ROLE.md — quyền chặn merge/release, DoD 9 điểm, phân loại lỗi 5 mức kèm ví dụ GoAn, 6 vùng rủi ro xếp theo thiệt hại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiến lược kiểm thử + hệ thống marker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chạy được từng nhóm test riêng; marker sai thì đỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 XONG: docs/QA/TEST_STRATEGY.md + 6 marker (unit/integration/api/security/money/prd) với --strict-markers. Ghi rõ cả những gì test tự động KHÔNG bắt được</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma trận truy vết PRD → test case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỗi yêu cầu PRD chỉ ra được test nào chứng minh nó đúng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiến lược kiểm thử</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 XONG: docs/QA/TRACEABILITY.md — 58 yêu cầu trích từ 3 tài liệu, 38 đã có test (66%), 2 còn thiếu có kế hoạch cụ thể, 18 thuộc P1/P2/P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mẫu báo lỗi + PR template bắt buộc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Báo lỗi có đủ bước tái hiện và request_id; MR phải trả lời 'test này đỏ khi nào'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 XONG: docs/QA/BUG_TEMPLATE.md + .github/pull_request_template.md. Sau mỗi sự cố bắt buộc viết test tái hiện TRƯỚC khi sửa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hạ tầng test: Redis giả, client API qua middleware thật, ngưỡng độ phủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test được cả tầng middleware và các nhánh fail-open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 XONG: tests/fakes.py (Redis giả có GEO + sorted set + cờ mô phỏng Redis chết), fixture api_client chạy qua đúng chuỗi middleware thật, CI có ngưỡng độ phủ 75% và job riêng cho nhóm money/security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trả nợ kiểm thử: matching và mã hoá CCCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 yêu cầu PRD có code nhưng chưa ai chứng minh đúng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hạ tầng test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 XONG: PRD-MATCH-01/02/03 (bán kính có nới thật, 2 tài xế cùng nhận chỉ 1 người thắng, chuyến quá hạn thoát trạng thái chờ) + PRD-SEC-05 (mã hoá CCCD). Tổng 51 → 129 test, độ phủ 78% → 81%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ĐÃ CÓ] Migration khởi tạo 18 bảng lõi</t>
   </si>
   <si>
@@ -822,7 +909,7 @@
     <t xml:space="preserve">Đã kiểm chứng: alembic/versions/0001_initial_schema.py, 18 create_table</t>
   </si>
   <si>
-    <t xml:space="preserve">P0-21</t>
+    <t xml:space="preserve">P0-27</t>
   </si>
   <si>
     <t xml:space="preserve">[ĐÃ CÓ] Bộ test tự động 51 test (pricing, escrow, fraud, payments, state machine, luồng chuyến)</t>
@@ -834,7 +921,7 @@
     <t xml:space="preserve">Đã kiểm chứng: chạy thật, 51 passed in 2.52s</t>
   </si>
   <si>
-    <t xml:space="preserve">P0-22</t>
+    <t xml:space="preserve">P0-28</t>
   </si>
   <si>
     <t xml:space="preserve">[ĐÃ CÓ] JSON structured logging + log_event</t>
@@ -987,9 +1074,6 @@
     <t xml:space="preserve">Đăng nhập, điều hướng, xử lý 401/403 hoàn chỉnh</t>
   </si>
   <si>
-    <t xml:space="preserve">FE</t>
-  </si>
-  <si>
     <t xml:space="preserve">P1-13</t>
   </si>
   <si>
@@ -1062,9 +1146,6 @@
     <t xml:space="preserve">P1-19</t>
   </si>
   <si>
-    <t xml:space="preserve">QA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bộ test case Console + kiểm thử phân quyền theo 12 vai trò</t>
   </si>
   <si>
@@ -2659,6 +2740,63 @@
   </si>
   <si>
     <t xml:space="preserve">pnpm install xanh (244 gói), pnpm build xanh, @goan/api-client typecheck sạch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399d8ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domains/audit: bảng audit_logs + middleware ghi mọi POST/PUT/PATCH/DELETE, che đệ quy 17 trường nhạy cảm, suy ra resource_type/resource_id từ đường dẫn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 test QA-AUD, gồm cả test payload lồng 50 tầng không làm treo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xoay vòng refresh token theo OAuth 2.0 BCP §4.13: dùng lại token đã tiêu thì thu hồi cả họ token của thiết bị đó. Thêm POST /auth/logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 test QA-AUTH, gồm kịch bản token bị đánh cắp và kịch bản không đá người dùng cũ ra khi deploy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">core/idempotency: middleware chung cho 5 nhóm endpoint chạm tiền. Gửi trùng phát lại response cũ, bản gốc đang chạy trả 409, chỉ cache kết quả thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 test QA-IDM chạy qua đúng chuỗi middleware thật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vận hành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X-Request-ID xuyên log, audit và response header; hook Sentry bật theo DSN, không gửi kèm PII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 test QA-RL/QA-OBS, gồm test /health không chạm DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dựng vai trò QA: quyền chặn merge/release, DoD 9 điểm, phân loại lỗi 5 mức, ma trận truy vết 58 yêu cầu PRD, mẫu báo lỗi và PR template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/QA/ 4 file; PR template bắt buộc trả lời câu 'test này đỏ khi nào'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trả 4 khoản nợ kiểm thử: bán kính matching có nới thật, 2 tài xế cùng nhận chỉ 1 người thắng, chuyến quá hạn thoát trạng thái chờ, mã hoá CCCD at-rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51 → 129 test, độ phủ 78% → 81%; CI thêm ngưỡng 75% và job riêng cho money/security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a1813a1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bàn giao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soạn MERGE_REQUEST.md: ánh xạ PRD, bảng 'test này đỏ khi nào', thay đổi phá vỡ tương thích, rủi ro và cách quay lui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhánh chore/p0-foundation, 5 commit. CHƯA push được: môi trường cầu nối không có thông tin đăng nhập GitHub</t>
   </si>
   <si>
     <t xml:space="preserve">ĐÁNH GIÁ BAN ĐẦU ĐÃ ĐƯỢC SỬA LẠI</t>
@@ -3884,40 +4022,40 @@
         <v>71</v>
       </c>
       <c r="B5" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5)</f>
-        <v>22</v>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A5)</f>
+        <v>28</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Đã xong")</f>
-        <v>11</v>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A5,Backlog!$K$5:$K$135,"Đã xong")</f>
+        <v>20</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Đang làm")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A5,Backlog!$K$5:$K$135,"Đang làm")</f>
+        <v>5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A5,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
+        <v>3</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A5,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A5,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A5)</f>
-        <v>46.5</v>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A5)</f>
+        <v>59.5</v>
       </c>
       <c r="H5" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A5)</f>
-        <v>25.65</v>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A5)</f>
+        <v>14.05</v>
       </c>
       <c r="I5" s="11" t="n">
         <f aca="false">IFERROR(1-H5/G5,1)</f>
-        <v>0.448387096774194</v>
+        <v>0.763865546218487</v>
       </c>
       <c r="J5" s="10" t="n">
         <f aca="false">IFERROR(ROUND(H5/$B$16,1),0)</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="8" t="str">
         <f aca="false">IF(F5&gt;0,"Có việc bị chặn",IF(I5&gt;=1,"Hoàn thành",IF(D5&gt;0,"Đang chạy","Chưa bắt đầu")))</f>
@@ -3929,31 +4067,31 @@
         <v>72</v>
       </c>
       <c r="B6" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A6)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A6)</f>
         <v>19</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A6,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A6,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D6" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A6,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A6,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A6,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A6,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>19</v>
       </c>
       <c r="F6" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A6,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A6,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A6)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A6)</f>
         <v>67</v>
       </c>
       <c r="H6" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A6)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A6)</f>
         <v>67</v>
       </c>
       <c r="I6" s="11" t="n">
@@ -3974,31 +4112,31 @@
         <v>73</v>
       </c>
       <c r="B7" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A7)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A7)</f>
         <v>21</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A7,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A7,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D7" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A7,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A7,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A7,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A7,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>21</v>
       </c>
       <c r="F7" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A7,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A7,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A7)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A7)</f>
         <v>70</v>
       </c>
       <c r="H7" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A7)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A7)</f>
         <v>70</v>
       </c>
       <c r="I7" s="11" t="n">
@@ -4019,31 +4157,31 @@
         <v>74</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A8)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A8)</f>
         <v>18</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A8,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A8,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A8,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A8,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A8,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A8,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>17</v>
       </c>
       <c r="F8" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A8,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A8,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>1</v>
       </c>
       <c r="G8" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A8)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A8)</f>
         <v>76</v>
       </c>
       <c r="H8" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A8)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A8)</f>
         <v>76</v>
       </c>
       <c r="I8" s="11" t="n">
@@ -4064,31 +4202,31 @@
         <v>75</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A9)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A9)</f>
         <v>13</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A9,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A9,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A9,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A9,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A9,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A9,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>13</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A9,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A9,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A9)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A9)</f>
         <v>47</v>
       </c>
       <c r="H9" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A9)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A9)</f>
         <v>47</v>
       </c>
       <c r="I9" s="11" t="n">
@@ -4109,31 +4247,31 @@
         <v>76</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A10)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A10)</f>
         <v>13</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A10,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A10,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A10,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A10,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A10,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A10,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>12</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A10,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A10,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A10)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A10)</f>
         <v>63</v>
       </c>
       <c r="H10" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A10)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A10)</f>
         <v>63</v>
       </c>
       <c r="I10" s="11" t="n">
@@ -4154,31 +4292,31 @@
         <v>77</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A11)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A11)</f>
         <v>11</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A11,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A11,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A11,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A11,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A11,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A11,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>11</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A11,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A11,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A11)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A11)</f>
         <v>41</v>
       </c>
       <c r="H11" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A11)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A11)</f>
         <v>41</v>
       </c>
       <c r="I11" s="11" t="n">
@@ -4199,31 +4337,31 @@
         <v>78</v>
       </c>
       <c r="B12" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A12)</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A12)</f>
         <v>8</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A12,Backlog!$K$5:$K$129,"Đã xong")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A12,Backlog!$K$5:$K$135,"Đã xong")</f>
         <v>0</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A12,Backlog!$K$5:$K$129,"Đang làm")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A12,Backlog!$K$5:$K$135,"Đang làm")</f>
         <v>0</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A12,Backlog!$K$5:$K$129,"Chưa bắt đầu")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A12,Backlog!$K$5:$K$135,"Chưa bắt đầu")</f>
         <v>8</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">COUNTIFS(Backlog!$B$5:$B$129,$A12,Backlog!$K$5:$K$129,"Bị chặn")</f>
+        <f aca="false">COUNTIFS(Backlog!$B$5:$B$135,$A12,Backlog!$K$5:$K$135,"Bị chặn")</f>
         <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$5:$H$129,Backlog!$B$5:$B$129,$A12)</f>
+        <f aca="false">SUMIFS(Backlog!$H$5:$H$135,Backlog!$B$5:$B$135,$A12)</f>
         <v>31</v>
       </c>
       <c r="H12" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$B$5:$B$129,$A12)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$B$5:$B$135,$A12)</f>
         <v>31</v>
       </c>
       <c r="I12" s="11" t="n">
@@ -4245,19 +4383,19 @@
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">SUM(B5:B12)</f>
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">SUM(C5:C12)</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">SUM(D5:D12)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">SUM(E5:E12)</f>
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">SUM(F5:F12)</f>
@@ -4265,19 +4403,19 @@
       </c>
       <c r="G13" s="14" t="n">
         <f aca="false">SUM(G5:G12)</f>
-        <v>441.5</v>
+        <v>454.5</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">SUM(H5:H12)</f>
-        <v>420.65</v>
+        <v>409.05</v>
       </c>
       <c r="I13" s="15" t="n">
         <f aca="false">IFERROR(1-H13/G13,0)</f>
-        <v>0.0472253680634203</v>
+        <v>0.1</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">IFERROR(ROUND(H13/$B$16,1),0)</f>
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="K13" s="12"/>
     </row>
@@ -4326,7 +4464,7 @@
       </c>
       <c r="B20" s="20" t="n">
         <f aca="false">ROUND(H13/B16,1)</f>
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>88</v>
@@ -4338,7 +4476,7 @@
       </c>
       <c r="B21" s="20" t="n">
         <f aca="false">ROUND(B20*B17,0)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -4355,7 +4493,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2CEBB846-36B4-4FEC-846A-80D84746E2C5}</x14:id>
+          <x14:id>{ED1EC020-2933-4E86-A999-B27730406997}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4376,7 +4514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2CEBB846-36B4-4FEC-846A-80D84746E2C5}">
+          <x14:cfRule type="dataBar" id="{ED1EC020-2933-4E86-A999-B27730406997}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4833,7 +4971,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6B432EDF-95A0-4095-872F-38F1D838D6F8}</x14:id>
+          <x14:id>{95CEDF3F-D4C5-4668-ADC4-C072625798A8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4860,7 +4998,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6B432EDF-95A0-4095-872F-38F1D838D6F8}">
+          <x14:cfRule type="dataBar" id="{95CEDF3F-D4C5-4668-ADC4-C072625798A8}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4885,7 +5023,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -5503,7 +5641,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
         <v>230</v>
       </c>
@@ -5531,21 +5669,21 @@
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L17" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="25" t="n">
         <f aca="false">H17*(1-L17)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" s="24"/>
       <c r="O17" s="21" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
         <v>234</v>
       </c>
@@ -5573,14 +5711,14 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L18" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="25" t="n">
         <f aca="false">H18*(1-L18)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N18" s="24"/>
       <c r="O18" s="21" t="s">
@@ -5631,7 +5769,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
         <v>243</v>
       </c>
@@ -5661,14 +5799,14 @@
         <v>246</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L20" s="26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M20" s="25" t="n">
         <f aca="false">H20*(1-L20)</f>
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="N20" s="24"/>
       <c r="O20" s="21" t="s">
@@ -5761,7 +5899,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
         <v>256</v>
       </c>
@@ -5789,40 +5927,42 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L23" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="25" t="n">
         <f aca="false">H23*(1-L23)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" s="24"/>
-      <c r="O23" s="21"/>
-    </row>
-    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O23" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B24" s="21" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="24" t="s">
         <v>38</v>
@@ -5840,31 +5980,31 @@
       </c>
       <c r="N24" s="24"/>
       <c r="O24" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>71</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D25" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="F25" s="24" t="s">
         <v>264</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" s="24" t="s">
         <v>38</v>
@@ -5882,36 +6022,38 @@
       </c>
       <c r="N25" s="24"/>
       <c r="O25" s="21" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B26" s="21" t="s">
         <v>71</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="21"/>
+        <v>38</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>273</v>
+      </c>
       <c r="K26" s="24" t="s">
         <v>29</v>
       </c>
@@ -5924,268 +6066,266 @@
       </c>
       <c r="N26" s="24"/>
       <c r="O26" s="21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="J27" s="21" t="s">
-        <v>274</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J27" s="21"/>
       <c r="K27" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L27" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="25" t="n">
         <f aca="false">H27*(1-L27)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" s="24"/>
       <c r="O27" s="21" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J28" s="21" t="s">
-        <v>279</v>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="25" t="n">
         <f aca="false">H28*(1-L28)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N28" s="24"/>
-      <c r="O28" s="21"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O28" s="21" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="24" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F29" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J29" s="21" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K29" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L29" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="25" t="n">
         <f aca="false">H29*(1-L29)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N29" s="24"/>
-      <c r="O29" s="21"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O29" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>196</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F30" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="21" t="s">
-        <v>286</v>
-      </c>
+      <c r="J30" s="21"/>
       <c r="K30" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L30" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="25" t="n">
         <f aca="false">H30*(1-L30)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" s="24"/>
-      <c r="O30" s="21"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O30" s="21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>196</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F31" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>290</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="J31" s="21"/>
       <c r="K31" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L31" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="25" t="n">
         <f aca="false">H31*(1-L31)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31" s="24"/>
-      <c r="O31" s="21"/>
-    </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O31" s="21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="21" t="s">
         <v>196</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F32" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>286</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J32" s="21"/>
       <c r="K32" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L32" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="25" t="n">
         <f aca="false">H32*(1-L32)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N32" s="24"/>
       <c r="O32" s="21" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="24" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B33" s="21" t="s">
         <v>72</v>
@@ -6194,23 +6334,23 @@
         <v>196</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F33" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G33" s="21"/>
       <c r="H33" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I33" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J33" s="21" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="K33" s="24" t="s">
         <v>33</v>
@@ -6220,14 +6360,16 @@
       </c>
       <c r="M33" s="25" t="n">
         <f aca="false">H33*(1-L33)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N33" s="24"/>
-      <c r="O33" s="21"/>
+      <c r="O33" s="21" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>72</v>
@@ -6236,10 +6378,10 @@
         <v>196</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F34" s="24" t="s">
         <v>188</v>
@@ -6252,7 +6394,7 @@
         <v>38</v>
       </c>
       <c r="J34" s="21" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="K34" s="24" t="s">
         <v>33</v>
@@ -6265,13 +6407,11 @@
         <v>4</v>
       </c>
       <c r="N34" s="24"/>
-      <c r="O34" s="21" t="s">
-        <v>301</v>
-      </c>
+      <c r="O34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="24" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B35" s="21" t="s">
         <v>72</v>
@@ -6280,23 +6420,23 @@
         <v>196</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F35" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G35" s="21"/>
       <c r="H35" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J35" s="21" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K35" s="24" t="s">
         <v>33</v>
@@ -6306,16 +6446,14 @@
       </c>
       <c r="M35" s="25" t="n">
         <f aca="false">H35*(1-L35)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N35" s="24"/>
-      <c r="O35" s="21" t="s">
-        <v>306</v>
-      </c>
+      <c r="O35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="24" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B36" s="21" t="s">
         <v>72</v>
@@ -6324,10 +6462,10 @@
         <v>196</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F36" s="24" t="s">
         <v>188</v>
@@ -6340,7 +6478,7 @@
         <v>38</v>
       </c>
       <c r="J36" s="21" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="K36" s="24" t="s">
         <v>33</v>
@@ -6357,7 +6495,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="24" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B37" s="21" t="s">
         <v>72</v>
@@ -6366,23 +6504,23 @@
         <v>196</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F37" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G37" s="21"/>
       <c r="H37" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="K37" s="24" t="s">
         <v>33</v>
@@ -6392,41 +6530,39 @@
       </c>
       <c r="M37" s="25" t="n">
         <f aca="false">H37*(1-L37)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" s="24"/>
-      <c r="O37" s="21" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B38" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G38" s="21"/>
       <c r="H38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J38" s="21" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="K38" s="24" t="s">
         <v>33</v>
@@ -6436,39 +6572,41 @@
       </c>
       <c r="M38" s="25" t="n">
         <f aca="false">H38*(1-L38)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38" s="24"/>
-      <c r="O38" s="21"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O38" s="21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B39" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G39" s="21"/>
       <c r="H39" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I39" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="K39" s="24" t="s">
         <v>33</v>
@@ -6478,39 +6616,39 @@
       </c>
       <c r="M39" s="25" t="n">
         <f aca="false">H39*(1-L39)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N39" s="24"/>
       <c r="O39" s="21"/>
     </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B40" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J40" s="21" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="K40" s="24" t="s">
         <v>33</v>
@@ -6523,26 +6661,28 @@
         <v>4</v>
       </c>
       <c r="N40" s="24"/>
-      <c r="O40" s="21"/>
-    </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O40" s="21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="24" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B41" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G41" s="21"/>
       <c r="H41" s="25" t="n">
@@ -6552,7 +6692,7 @@
         <v>38</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K41" s="24" t="s">
         <v>33</v>
@@ -6565,36 +6705,38 @@
         <v>4</v>
       </c>
       <c r="N41" s="24"/>
-      <c r="O41" s="21"/>
+      <c r="O41" s="21" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="24" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B42" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I42" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J42" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K42" s="24" t="s">
         <v>33</v>
@@ -6604,39 +6746,39 @@
       </c>
       <c r="M42" s="25" t="n">
         <f aca="false">H42*(1-L42)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N42" s="24"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="24" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B43" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G43" s="21"/>
       <c r="H43" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K43" s="24" t="s">
         <v>33</v>
@@ -6646,39 +6788,41 @@
       </c>
       <c r="M43" s="25" t="n">
         <f aca="false">H43*(1-L43)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" s="24"/>
-      <c r="O43" s="21"/>
+      <c r="O43" s="21" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="24" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B44" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G44" s="21"/>
       <c r="H44" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J44" s="21" t="s">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="K44" s="24" t="s">
         <v>33</v>
@@ -6688,39 +6832,39 @@
       </c>
       <c r="M44" s="25" t="n">
         <f aca="false">H44*(1-L44)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44" s="24"/>
       <c r="O44" s="21"/>
     </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="24" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B45" s="21" t="s">
         <v>72</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G45" s="21"/>
       <c r="H45" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J45" s="21" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K45" s="24" t="s">
         <v>33</v>
@@ -6730,36 +6874,36 @@
       </c>
       <c r="M45" s="25" t="n">
         <f aca="false">H45*(1-L45)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N45" s="24"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="24" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G46" s="21"/>
       <c r="H46" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J46" s="21" t="s">
         <v>350</v>
@@ -6775,28 +6919,26 @@
         <v>4</v>
       </c>
       <c r="N46" s="24"/>
-      <c r="O46" s="21" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O46" s="21"/>
+    </row>
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="24" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G47" s="21"/>
       <c r="H47" s="25" t="n">
@@ -6806,7 +6948,7 @@
         <v>38</v>
       </c>
       <c r="J47" s="21" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K47" s="24" t="s">
         <v>33</v>
@@ -6823,32 +6965,32 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G48" s="21"/>
       <c r="H48" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K48" s="24" t="s">
         <v>33</v>
@@ -6858,39 +7000,39 @@
       </c>
       <c r="M48" s="25" t="n">
         <f aca="false">H48*(1-L48)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N48" s="24"/>
       <c r="O48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="24" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G49" s="21"/>
       <c r="H49" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K49" s="24" t="s">
         <v>33</v>
@@ -6900,39 +7042,39 @@
       </c>
       <c r="M49" s="25" t="n">
         <f aca="false">H49*(1-L49)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N49" s="24"/>
       <c r="O49" s="21"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G50" s="21"/>
       <c r="H50" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J50" s="21" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="K50" s="24" t="s">
         <v>33</v>
@@ -6942,39 +7084,39 @@
       </c>
       <c r="M50" s="25" t="n">
         <f aca="false">H50*(1-L50)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N50" s="24"/>
       <c r="O50" s="21"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="24" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G51" s="21"/>
       <c r="H51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="K51" s="24" t="s">
         <v>33</v>
@@ -6984,16 +7126,14 @@
       </c>
       <c r="M51" s="25" t="n">
         <f aca="false">H51*(1-L51)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51" s="24"/>
-      <c r="O51" s="21" t="s">
-        <v>369</v>
-      </c>
+      <c r="O51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B52" s="21" t="s">
         <v>73</v>
@@ -7002,23 +7142,23 @@
         <v>196</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F52" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G52" s="21"/>
       <c r="H52" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J52" s="21" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="K52" s="24" t="s">
         <v>33</v>
@@ -7028,14 +7168,16 @@
       </c>
       <c r="M52" s="25" t="n">
         <f aca="false">H52*(1-L52)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N52" s="24"/>
-      <c r="O52" s="21"/>
-    </row>
-    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O52" s="21" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="24" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B53" s="21" t="s">
         <v>73</v>
@@ -7044,23 +7186,23 @@
         <v>196</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F53" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G53" s="21"/>
       <c r="H53" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I53" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="K53" s="24" t="s">
         <v>33</v>
@@ -7070,14 +7212,14 @@
       </c>
       <c r="M53" s="25" t="n">
         <f aca="false">H53*(1-L53)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N53" s="24"/>
       <c r="O53" s="21"/>
     </row>
-    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="24" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B54" s="21" t="s">
         <v>73</v>
@@ -7086,10 +7228,10 @@
         <v>196</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F54" s="24" t="s">
         <v>188</v>
@@ -7099,10 +7241,10 @@
         <v>3</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J54" s="21" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="K54" s="24" t="s">
         <v>33</v>
@@ -7119,7 +7261,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="24" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B55" s="21" t="s">
         <v>73</v>
@@ -7128,10 +7270,10 @@
         <v>196</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F55" s="24" t="s">
         <v>188</v>
@@ -7141,10 +7283,10 @@
         <v>2</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J55" s="21" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="K55" s="24" t="s">
         <v>33</v>
@@ -7159,9 +7301,9 @@
       <c r="N55" s="24"/>
       <c r="O55" s="21"/>
     </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B56" s="21" t="s">
         <v>73</v>
@@ -7170,23 +7312,23 @@
         <v>196</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F56" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G56" s="21"/>
       <c r="H56" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J56" s="21" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="K56" s="24" t="s">
         <v>33</v>
@@ -7196,16 +7338,14 @@
       </c>
       <c r="M56" s="25" t="n">
         <f aca="false">H56*(1-L56)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" s="24"/>
-      <c r="O56" s="21" t="s">
-        <v>386</v>
-      </c>
+      <c r="O56" s="21"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="24" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>73</v>
@@ -7214,23 +7354,23 @@
         <v>196</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="F57" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G57" s="21"/>
       <c r="H57" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J57" s="21" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="K57" s="24" t="s">
         <v>33</v>
@@ -7240,14 +7380,16 @@
       </c>
       <c r="M57" s="25" t="n">
         <f aca="false">H57*(1-L57)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N57" s="24"/>
-      <c r="O57" s="21"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O57" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="24" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B58" s="21" t="s">
         <v>73</v>
@@ -7256,23 +7398,23 @@
         <v>196</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F58" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G58" s="21"/>
       <c r="H58" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="K58" s="24" t="s">
         <v>33</v>
@@ -7282,16 +7424,14 @@
       </c>
       <c r="M58" s="25" t="n">
         <f aca="false">H58*(1-L58)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58" s="24"/>
-      <c r="O58" s="21" t="s">
-        <v>393</v>
-      </c>
+      <c r="O58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="24" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B59" s="21" t="s">
         <v>73</v>
@@ -7300,23 +7440,23 @@
         <v>196</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F59" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G59" s="21"/>
       <c r="H59" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="K59" s="24" t="s">
         <v>33</v>
@@ -7326,41 +7466,39 @@
       </c>
       <c r="M59" s="25" t="n">
         <f aca="false">H59*(1-L59)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N59" s="24"/>
-      <c r="O59" s="21" t="s">
-        <v>397</v>
-      </c>
+      <c r="O59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="24" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B60" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G60" s="21"/>
       <c r="H60" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J60" s="21" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K60" s="24" t="s">
         <v>33</v>
@@ -7370,39 +7508,39 @@
       </c>
       <c r="M60" s="25" t="n">
         <f aca="false">H60*(1-L60)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N60" s="24"/>
       <c r="O60" s="21"/>
     </row>
-    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="24" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B61" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G61" s="21"/>
       <c r="H61" s="25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="K61" s="24" t="s">
         <v>33</v>
@@ -7412,39 +7550,39 @@
       </c>
       <c r="M61" s="25" t="n">
         <f aca="false">H61*(1-L61)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N61" s="24"/>
       <c r="O61" s="21"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="24" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B62" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G62" s="21"/>
       <c r="H62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="K62" s="24" t="s">
         <v>33</v>
@@ -7454,39 +7592,41 @@
       </c>
       <c r="M62" s="25" t="n">
         <f aca="false">H62*(1-L62)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N62" s="24"/>
-      <c r="O62" s="21"/>
-    </row>
-    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O62" s="21" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B63" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G63" s="21"/>
       <c r="H63" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I63" s="24" t="s">
         <v>40</v>
       </c>
       <c r="J63" s="21" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="K63" s="24" t="s">
         <v>33</v>
@@ -7496,39 +7636,39 @@
       </c>
       <c r="M63" s="25" t="n">
         <f aca="false">H63*(1-L63)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N63" s="24"/>
       <c r="O63" s="21"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="24" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B64" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G64" s="21"/>
       <c r="H64" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J64" s="21" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="K64" s="24" t="s">
         <v>33</v>
@@ -7538,14 +7678,16 @@
       </c>
       <c r="M64" s="25" t="n">
         <f aca="false">H64*(1-L64)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N64" s="24"/>
-      <c r="O64" s="21"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O64" s="21" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B65" s="21" t="s">
         <v>73</v>
@@ -7554,23 +7696,23 @@
         <v>196</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F65" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G65" s="21"/>
       <c r="H65" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J65" s="21" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="K65" s="24" t="s">
         <v>33</v>
@@ -7580,39 +7722,41 @@
       </c>
       <c r="M65" s="25" t="n">
         <f aca="false">H65*(1-L65)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N65" s="24"/>
-      <c r="O65" s="21"/>
+      <c r="O65" s="21" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="24" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B66" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G66" s="21"/>
       <c r="H66" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I66" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="K66" s="24" t="s">
         <v>33</v>
@@ -7622,39 +7766,39 @@
       </c>
       <c r="M66" s="25" t="n">
         <f aca="false">H66*(1-L66)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N66" s="24"/>
       <c r="O66" s="21"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="24" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>423</v>
+        <v>344</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="G67" s="21"/>
       <c r="H67" s="25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I67" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J67" s="21" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="K67" s="24" t="s">
         <v>33</v>
@@ -7664,41 +7808,39 @@
       </c>
       <c r="M67" s="25" t="n">
         <f aca="false">H67*(1-L67)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N67" s="24"/>
-      <c r="O67" s="21" t="s">
-        <v>428</v>
-      </c>
+      <c r="O67" s="21"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="24" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>423</v>
+        <v>344</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="G68" s="21"/>
       <c r="H68" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K68" s="24" t="s">
         <v>33</v>
@@ -7708,39 +7850,39 @@
       </c>
       <c r="M68" s="25" t="n">
         <f aca="false">H68*(1-L68)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68" s="24"/>
       <c r="O68" s="21"/>
     </row>
     <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="24" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>423</v>
+        <v>344</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E69" s="21" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F69" s="24" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="G69" s="21"/>
       <c r="H69" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J69" s="21" t="s">
-        <v>337</v>
+        <v>386</v>
       </c>
       <c r="K69" s="24" t="s">
         <v>33</v>
@@ -7750,38 +7892,40 @@
       </c>
       <c r="M69" s="25" t="n">
         <f aca="false">H69*(1-L69)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N69" s="24"/>
       <c r="O69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="24" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G70" s="21"/>
       <c r="H70" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="J70" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="J70" s="21" t="s">
+        <v>406</v>
+      </c>
       <c r="K70" s="24" t="s">
         <v>33</v>
       </c>
@@ -7790,41 +7934,39 @@
       </c>
       <c r="M70" s="25" t="n">
         <f aca="false">H70*(1-L70)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N70" s="24"/>
-      <c r="O70" s="21" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O70" s="21"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="24" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>426</v>
+        <v>188</v>
       </c>
       <c r="G71" s="21"/>
       <c r="H71" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J71" s="21" t="s">
-        <v>443</v>
+        <v>382</v>
       </c>
       <c r="K71" s="24" t="s">
         <v>33</v>
@@ -7834,22 +7976,20 @@
       </c>
       <c r="M71" s="25" t="n">
         <f aca="false">H71*(1-L71)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N71" s="24"/>
-      <c r="O71" s="21" t="s">
-        <v>444</v>
-      </c>
+      <c r="O71" s="21"/>
     </row>
     <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="24" t="s">
         <v>445</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>423</v>
+        <v>261</v>
       </c>
       <c r="D72" s="21" t="s">
         <v>446</v>
@@ -7858,11 +7998,11 @@
         <v>447</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="G72" s="21"/>
       <c r="H72" s="25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I72" s="24" t="s">
         <v>38</v>
@@ -7871,29 +8011,27 @@
         <v>448</v>
       </c>
       <c r="K72" s="24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L72" s="26" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="25" t="n">
         <f aca="false">H72*(1-L72)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N72" s="24"/>
-      <c r="O72" s="21" t="s">
-        <v>449</v>
-      </c>
+      <c r="O72" s="21"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B73" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D73" s="21" t="s">
         <v>451</v>
@@ -7902,7 +8040,7 @@
         <v>452</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G73" s="21"/>
       <c r="H73" s="25" t="n">
@@ -7912,7 +8050,7 @@
         <v>38</v>
       </c>
       <c r="J73" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K73" s="24" t="s">
         <v>33</v>
@@ -7926,37 +8064,37 @@
       </c>
       <c r="N73" s="24"/>
       <c r="O73" s="21" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B74" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G74" s="21"/>
       <c r="H74" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I74" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J74" s="21" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K74" s="24" t="s">
         <v>33</v>
@@ -7966,39 +8104,39 @@
       </c>
       <c r="M74" s="25" t="n">
         <f aca="false">H74*(1-L74)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N74" s="24"/>
       <c r="O74" s="21"/>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B75" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G75" s="21"/>
       <c r="H75" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I75" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J75" s="21" t="s">
-        <v>432</v>
+        <v>365</v>
       </c>
       <c r="K75" s="24" t="s">
         <v>33</v>
@@ -8008,14 +8146,12 @@
       </c>
       <c r="M75" s="25" t="n">
         <f aca="false">H75*(1-L75)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N75" s="24"/>
-      <c r="O75" s="21" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O75" s="21"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
         <v>463</v>
       </c>
@@ -8023,7 +8159,7 @@
         <v>74</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="D76" s="21" t="s">
         <v>464</v>
@@ -8032,7 +8168,7 @@
         <v>465</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>426</v>
+        <v>188</v>
       </c>
       <c r="G76" s="21"/>
       <c r="H76" s="25" t="n">
@@ -8041,9 +8177,7 @@
       <c r="I76" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J76" s="21" t="s">
-        <v>453</v>
-      </c>
+      <c r="J76" s="21"/>
       <c r="K76" s="24" t="s">
         <v>33</v>
       </c>
@@ -8059,7 +8193,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24" t="s">
         <v>467</v>
       </c>
@@ -8067,7 +8201,7 @@
         <v>74</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D77" s="21" t="s">
         <v>468</v>
@@ -8076,17 +8210,17 @@
         <v>469</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G77" s="21"/>
       <c r="H77" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J77" s="21" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="K77" s="24" t="s">
         <v>33</v>
@@ -8096,71 +8230,75 @@
       </c>
       <c r="M77" s="25" t="n">
         <f aca="false">H77*(1-L77)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77" s="24"/>
-      <c r="O77" s="21"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O77" s="21" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B78" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G78" s="21"/>
       <c r="H78" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I78" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J78" s="21" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="K78" s="24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L78" s="26" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="25" t="n">
         <f aca="false">H78*(1-L78)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N78" s="24"/>
-      <c r="O78" s="21"/>
+      <c r="O78" s="21" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="24" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B79" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G79" s="21"/>
       <c r="H79" s="25" t="n">
@@ -8170,7 +8308,7 @@
         <v>38</v>
       </c>
       <c r="J79" s="21" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K79" s="24" t="s">
         <v>33</v>
@@ -8183,36 +8321,38 @@
         <v>4</v>
       </c>
       <c r="N79" s="24"/>
-      <c r="O79" s="21"/>
-    </row>
-    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O79" s="21" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="24" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B80" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G80" s="21"/>
       <c r="H80" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I80" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J80" s="21" t="s">
-        <v>379</v>
+        <v>485</v>
       </c>
       <c r="K80" s="24" t="s">
         <v>33</v>
@@ -8222,29 +8362,29 @@
       </c>
       <c r="M80" s="25" t="n">
         <f aca="false">H80*(1-L80)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N80" s="24"/>
       <c r="O80" s="21"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="24" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B81" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E81" s="21" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G81" s="21"/>
       <c r="H81" s="25" t="n">
@@ -8254,7 +8394,7 @@
         <v>38</v>
       </c>
       <c r="J81" s="21" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="K81" s="24" t="s">
         <v>33</v>
@@ -8267,26 +8407,28 @@
         <v>4</v>
       </c>
       <c r="N81" s="24"/>
-      <c r="O81" s="21"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O81" s="21" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="24" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B82" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>196</v>
+        <v>450</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>188</v>
+        <v>453</v>
       </c>
       <c r="G82" s="21"/>
       <c r="H82" s="25" t="n">
@@ -8296,7 +8438,7 @@
         <v>38</v>
       </c>
       <c r="J82" s="21" t="s">
-        <v>305</v>
+        <v>480</v>
       </c>
       <c r="K82" s="24" t="s">
         <v>33</v>
@@ -8309,26 +8451,28 @@
         <v>4</v>
       </c>
       <c r="N82" s="24"/>
-      <c r="O82" s="21"/>
+      <c r="O82" s="21" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="24" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B83" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E83" s="21" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G83" s="21"/>
       <c r="H83" s="25" t="n">
@@ -8338,7 +8482,7 @@
         <v>38</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="K83" s="24" t="s">
         <v>33</v>
@@ -8353,24 +8497,24 @@
       <c r="N83" s="24"/>
       <c r="O83" s="21"/>
     </row>
-    <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="24" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B84" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>343</v>
+        <v>450</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>318</v>
+        <v>453</v>
       </c>
       <c r="G84" s="21"/>
       <c r="H84" s="25" t="n">
@@ -8380,7 +8524,7 @@
         <v>38</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="K84" s="24" t="s">
         <v>33</v>
@@ -8395,34 +8539,34 @@
       <c r="N84" s="24"/>
       <c r="O84" s="21"/>
     </row>
-    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="24" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E85" s="21" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G85" s="21"/>
       <c r="H85" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I85" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="K85" s="24" t="s">
         <v>33</v>
@@ -8432,39 +8576,39 @@
       </c>
       <c r="M85" s="25" t="n">
         <f aca="false">H85*(1-L85)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N85" s="24"/>
       <c r="O85" s="21"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="24" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G86" s="21"/>
       <c r="H86" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="K86" s="24" t="s">
         <v>33</v>
@@ -8474,39 +8618,39 @@
       </c>
       <c r="M86" s="25" t="n">
         <f aca="false">H86*(1-L86)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N86" s="24"/>
       <c r="O86" s="21"/>
     </row>
-    <row r="87" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="24" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G87" s="21"/>
       <c r="H87" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I87" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J87" s="21" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="K87" s="24" t="s">
         <v>33</v>
@@ -8516,41 +8660,39 @@
       </c>
       <c r="M87" s="25" t="n">
         <f aca="false">H87*(1-L87)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N87" s="24"/>
-      <c r="O87" s="21" t="s">
-        <v>505</v>
-      </c>
+      <c r="O87" s="21"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="24" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>426</v>
+        <v>188</v>
       </c>
       <c r="G88" s="21"/>
       <c r="H88" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I88" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>476</v>
+        <v>334</v>
       </c>
       <c r="K88" s="24" t="s">
         <v>33</v>
@@ -8560,39 +8702,39 @@
       </c>
       <c r="M88" s="25" t="n">
         <f aca="false">H88*(1-L88)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N88" s="24"/>
       <c r="O88" s="21"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="24" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G89" s="21"/>
       <c r="H89" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J89" s="21" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="K89" s="24" t="s">
         <v>33</v>
@@ -8602,31 +8744,29 @@
       </c>
       <c r="M89" s="25" t="n">
         <f aca="false">H89*(1-L89)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N89" s="24"/>
-      <c r="O89" s="21" t="s">
-        <v>512</v>
-      </c>
+      <c r="O89" s="21"/>
     </row>
     <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="24" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>423</v>
+        <v>261</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="G90" s="21"/>
       <c r="H90" s="25" t="n">
@@ -8636,7 +8776,7 @@
         <v>38</v>
       </c>
       <c r="J90" s="21" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K90" s="24" t="s">
         <v>33</v>
@@ -8651,34 +8791,34 @@
       <c r="N90" s="24"/>
       <c r="O90" s="21"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="24" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G91" s="21"/>
       <c r="H91" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I91" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J91" s="21" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="K91" s="24" t="s">
         <v>33</v>
@@ -8688,39 +8828,39 @@
       </c>
       <c r="M91" s="25" t="n">
         <f aca="false">H91*(1-L91)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N91" s="24"/>
       <c r="O91" s="21"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="24" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B92" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F92" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G92" s="21"/>
       <c r="H92" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I92" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J92" s="21" t="s">
-        <v>476</v>
+        <v>528</v>
       </c>
       <c r="K92" s="24" t="s">
         <v>33</v>
@@ -8730,39 +8870,39 @@
       </c>
       <c r="M92" s="25" t="n">
         <f aca="false">H92*(1-L92)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N92" s="24"/>
       <c r="O92" s="21"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="24" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B93" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="E93" s="21" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G93" s="21"/>
       <c r="H93" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I93" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J93" s="21" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K93" s="24" t="s">
         <v>33</v>
@@ -8772,39 +8912,41 @@
       </c>
       <c r="M93" s="25" t="n">
         <f aca="false">H93*(1-L93)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N93" s="24"/>
-      <c r="O93" s="21"/>
+      <c r="O93" s="21" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="24" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B94" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G94" s="21"/>
       <c r="H94" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I94" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J94" s="21" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="K94" s="24" t="s">
         <v>33</v>
@@ -8814,41 +8956,39 @@
       </c>
       <c r="M94" s="25" t="n">
         <f aca="false">H94*(1-L94)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N94" s="24"/>
-      <c r="O94" s="21" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O94" s="21"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="24" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B95" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>196</v>
+        <v>450</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E95" s="21" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>188</v>
+        <v>453</v>
       </c>
       <c r="G95" s="21"/>
       <c r="H95" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I95" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J95" s="21" t="s">
-        <v>305</v>
+        <v>528</v>
       </c>
       <c r="K95" s="24" t="s">
         <v>33</v>
@@ -8858,41 +8998,41 @@
       </c>
       <c r="M95" s="25" t="n">
         <f aca="false">H95*(1-L95)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N95" s="24"/>
       <c r="O95" s="21" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="24" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B96" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>315</v>
+        <v>450</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>318</v>
+        <v>453</v>
       </c>
       <c r="G96" s="21"/>
       <c r="H96" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J96" s="21" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K96" s="24" t="s">
         <v>33</v>
@@ -8902,31 +9042,29 @@
       </c>
       <c r="M96" s="25" t="n">
         <f aca="false">H96*(1-L96)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N96" s="24"/>
-      <c r="O96" s="21" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O96" s="21"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="24" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B97" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>343</v>
+        <v>450</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E97" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>318</v>
+        <v>453</v>
       </c>
       <c r="G97" s="21"/>
       <c r="H97" s="25" t="n">
@@ -8936,7 +9074,7 @@
         <v>38</v>
       </c>
       <c r="J97" s="21" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="K97" s="24" t="s">
         <v>33</v>
@@ -8951,34 +9089,34 @@
       <c r="N97" s="24"/>
       <c r="O97" s="21"/>
     </row>
-    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="24" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>196</v>
+        <v>450</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>179</v>
+        <v>453</v>
       </c>
       <c r="G98" s="21"/>
       <c r="H98" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I98" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J98" s="21" t="s">
-        <v>427</v>
+        <v>503</v>
       </c>
       <c r="K98" s="24" t="s">
         <v>33</v>
@@ -8988,41 +9126,39 @@
       </c>
       <c r="M98" s="25" t="n">
         <f aca="false">H98*(1-L98)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N98" s="24"/>
-      <c r="O98" s="21" t="s">
-        <v>549</v>
-      </c>
+      <c r="O98" s="21"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="24" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>196</v>
+        <v>450</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E99" s="21" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>188</v>
+        <v>453</v>
       </c>
       <c r="G99" s="21"/>
       <c r="H99" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I99" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J99" s="21" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K99" s="24" t="s">
         <v>33</v>
@@ -9032,39 +9168,39 @@
       </c>
       <c r="M99" s="25" t="n">
         <f aca="false">H99*(1-L99)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N99" s="24"/>
       <c r="O99" s="21"/>
     </row>
-    <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="24" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>196</v>
+        <v>450</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>188</v>
+        <v>453</v>
       </c>
       <c r="G100" s="21"/>
       <c r="H100" s="25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I100" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J100" s="21" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K100" s="24" t="s">
         <v>33</v>
@@ -9074,39 +9210,41 @@
       </c>
       <c r="M100" s="25" t="n">
         <f aca="false">H100*(1-L100)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N100" s="24"/>
-      <c r="O100" s="21"/>
+      <c r="O100" s="21" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="24" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C101" s="21" t="s">
         <v>196</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E101" s="21" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F101" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G101" s="21"/>
       <c r="H101" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I101" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J101" s="21" t="s">
-        <v>561</v>
+        <v>334</v>
       </c>
       <c r="K101" s="24" t="s">
         <v>33</v>
@@ -9116,41 +9254,41 @@
       </c>
       <c r="M101" s="25" t="n">
         <f aca="false">H101*(1-L101)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N101" s="24"/>
       <c r="O101" s="21" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="24" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G102" s="21"/>
       <c r="H102" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I102" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J102" s="21" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="K102" s="24" t="s">
         <v>33</v>
@@ -9160,41 +9298,41 @@
       </c>
       <c r="M102" s="25" t="n">
         <f aca="false">H102*(1-L102)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N102" s="24"/>
       <c r="O102" s="21" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="24" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E103" s="21" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F103" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G103" s="21"/>
       <c r="H103" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I103" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J103" s="21" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="K103" s="24" t="s">
         <v>33</v>
@@ -9204,16 +9342,14 @@
       </c>
       <c r="M103" s="25" t="n">
         <f aca="false">H103*(1-L103)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N103" s="24"/>
-      <c r="O103" s="21" t="s">
-        <v>570</v>
-      </c>
+      <c r="O103" s="21"/>
     </row>
     <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="24" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B104" s="21" t="s">
         <v>76</v>
@@ -9222,22 +9358,24 @@
         <v>196</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F104" s="24" t="s">
         <v>179</v>
       </c>
       <c r="G104" s="21"/>
       <c r="H104" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I104" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J104" s="21"/>
+      <c r="J104" s="21" t="s">
+        <v>454</v>
+      </c>
       <c r="K104" s="24" t="s">
         <v>33</v>
       </c>
@@ -9246,16 +9384,16 @@
       </c>
       <c r="M104" s="25" t="n">
         <f aca="false">H104*(1-L104)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N104" s="24"/>
       <c r="O104" s="21" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="24" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B105" s="21" t="s">
         <v>76</v>
@@ -9264,23 +9402,23 @@
         <v>196</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E105" s="21" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="F105" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G105" s="21"/>
       <c r="H105" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I105" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J105" s="21" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="K105" s="24" t="s">
         <v>33</v>
@@ -9290,16 +9428,14 @@
       </c>
       <c r="M105" s="25" t="n">
         <f aca="false">H105*(1-L105)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N105" s="24"/>
-      <c r="O105" s="21" t="s">
-        <v>578</v>
-      </c>
+      <c r="O105" s="21"/>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="24" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B106" s="21" t="s">
         <v>76</v>
@@ -9308,42 +9444,40 @@
         <v>196</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E106" s="21" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F106" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G106" s="21"/>
       <c r="H106" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I106" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J106" s="21" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="K106" s="24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L106" s="26" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="25" t="n">
         <f aca="false">H106*(1-L106)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N106" s="24"/>
-      <c r="O106" s="21" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O106" s="21"/>
+    </row>
+    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="24" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B107" s="21" t="s">
         <v>76</v>
@@ -9352,23 +9486,23 @@
         <v>196</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F107" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G107" s="21"/>
       <c r="H107" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I107" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J107" s="21" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K107" s="24" t="s">
         <v>33</v>
@@ -9378,41 +9512,41 @@
       </c>
       <c r="M107" s="25" t="n">
         <f aca="false">H107*(1-L107)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N107" s="24"/>
       <c r="O107" s="21" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="24" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B108" s="21" t="s">
         <v>76</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G108" s="21"/>
       <c r="H108" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I108" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="K108" s="24" t="s">
         <v>33</v>
@@ -9422,39 +9556,41 @@
       </c>
       <c r="M108" s="25" t="n">
         <f aca="false">H108*(1-L108)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N108" s="24"/>
-      <c r="O108" s="21"/>
-    </row>
-    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O108" s="21" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="24" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B109" s="21" t="s">
         <v>76</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E109" s="21" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G109" s="21"/>
       <c r="H109" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I109" s="24" t="s">
         <v>40</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="K109" s="24" t="s">
         <v>33</v>
@@ -9464,40 +9600,40 @@
       </c>
       <c r="M109" s="25" t="n">
         <f aca="false">H109*(1-L109)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N109" s="24"/>
-      <c r="O109" s="21"/>
+      <c r="O109" s="21" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="24" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B110" s="21" t="s">
         <v>76</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>343</v>
+        <v>196</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E110" s="21" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="G110" s="21"/>
       <c r="H110" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I110" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J110" s="21" t="s">
-        <v>598</v>
-      </c>
+      <c r="J110" s="21"/>
       <c r="K110" s="24" t="s">
         <v>33</v>
       </c>
@@ -9506,39 +9642,41 @@
       </c>
       <c r="M110" s="25" t="n">
         <f aca="false">H110*(1-L110)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N110" s="24"/>
-      <c r="O110" s="21"/>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O110" s="21" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="24" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C111" s="21" t="s">
         <v>196</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E111" s="21" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F111" s="24" t="s">
         <v>188</v>
       </c>
       <c r="G111" s="21"/>
       <c r="H111" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I111" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J111" s="21" t="s">
-        <v>305</v>
+        <v>588</v>
       </c>
       <c r="K111" s="24" t="s">
         <v>33</v>
@@ -9548,83 +9686,85 @@
       </c>
       <c r="M111" s="25" t="n">
         <f aca="false">H111*(1-L111)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N111" s="24"/>
       <c r="O111" s="21" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="24" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E112" s="21" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G112" s="21"/>
       <c r="H112" s="25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I112" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J112" s="21" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="K112" s="24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L112" s="26" t="n">
         <v>0</v>
       </c>
       <c r="M112" s="25" t="n">
         <f aca="false">H112*(1-L112)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N112" s="24"/>
-      <c r="O112" s="21"/>
+      <c r="O112" s="21" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="24" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E113" s="21" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G113" s="21"/>
       <c r="H113" s="25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I113" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J113" s="21" t="s">
-        <v>531</v>
+        <v>613</v>
       </c>
       <c r="K113" s="24" t="s">
         <v>33</v>
@@ -9634,39 +9774,41 @@
       </c>
       <c r="M113" s="25" t="n">
         <f aca="false">H113*(1-L113)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N113" s="24"/>
-      <c r="O113" s="21"/>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O113" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="24" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E114" s="21" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G114" s="21"/>
       <c r="H114" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I114" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>531</v>
+        <v>618</v>
       </c>
       <c r="K114" s="24" t="s">
         <v>33</v>
@@ -9676,39 +9818,39 @@
       </c>
       <c r="M114" s="25" t="n">
         <f aca="false">H114*(1-L114)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N114" s="24"/>
       <c r="O114" s="21"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="24" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E115" s="21" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G115" s="21"/>
       <c r="H115" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I115" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J115" s="21" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="K115" s="24" t="s">
         <v>33</v>
@@ -9718,39 +9860,39 @@
       </c>
       <c r="M115" s="25" t="n">
         <f aca="false">H115*(1-L115)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N115" s="24"/>
       <c r="O115" s="21"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="24" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E116" s="21" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G116" s="21"/>
       <c r="H116" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I116" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>531</v>
+        <v>625</v>
       </c>
       <c r="K116" s="24" t="s">
         <v>33</v>
@@ -9765,34 +9907,34 @@
       <c r="N116" s="24"/>
       <c r="O116" s="21"/>
     </row>
-    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="24" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B117" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D117" s="21" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="E117" s="21" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="G117" s="21"/>
       <c r="H117" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I117" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J117" s="21" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="K117" s="24" t="s">
         <v>33</v>
@@ -9802,39 +9944,41 @@
       </c>
       <c r="M117" s="25" t="n">
         <f aca="false">H117*(1-L117)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N117" s="24"/>
-      <c r="O117" s="21"/>
-    </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O117" s="21" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="24" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B118" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="E118" s="21" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G118" s="21"/>
       <c r="H118" s="25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I118" s="24" t="s">
         <v>40</v>
       </c>
       <c r="J118" s="21" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="K118" s="24" t="s">
         <v>33</v>
@@ -9844,29 +9988,29 @@
       </c>
       <c r="M118" s="25" t="n">
         <f aca="false">H118*(1-L118)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N118" s="24"/>
       <c r="O118" s="21"/>
     </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="24" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B119" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="E119" s="21" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G119" s="21"/>
       <c r="H119" s="25" t="n">
@@ -9876,7 +10020,7 @@
         <v>40</v>
       </c>
       <c r="J119" s="21" t="s">
-        <v>305</v>
+        <v>558</v>
       </c>
       <c r="K119" s="24" t="s">
         <v>33</v>
@@ -9893,32 +10037,32 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="24" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="B120" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="E120" s="21" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="G120" s="21"/>
       <c r="H120" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I120" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J120" s="21" t="s">
-        <v>633</v>
+        <v>558</v>
       </c>
       <c r="K120" s="24" t="s">
         <v>33</v>
@@ -9928,39 +10072,39 @@
       </c>
       <c r="M120" s="25" t="n">
         <f aca="false">H120*(1-L120)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N120" s="24"/>
       <c r="O120" s="21"/>
     </row>
-    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="24" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="B121" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>179</v>
+        <v>344</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E121" s="21" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="G121" s="21"/>
       <c r="H121" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I121" s="24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J121" s="21" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="K121" s="24" t="s">
         <v>33</v>
@@ -9973,38 +10117,36 @@
         <v>2</v>
       </c>
       <c r="N121" s="24"/>
-      <c r="O121" s="21" t="s">
-        <v>637</v>
-      </c>
+      <c r="O121" s="21"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="24" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E122" s="21" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="G122" s="21"/>
       <c r="H122" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I122" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J122" s="21" t="s">
-        <v>641</v>
+        <v>558</v>
       </c>
       <c r="K122" s="24" t="s">
         <v>33</v>
@@ -10014,39 +10156,39 @@
       </c>
       <c r="M122" s="25" t="n">
         <f aca="false">H122*(1-L122)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N122" s="24"/>
       <c r="O122" s="21"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="24" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E123" s="21" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="G123" s="21"/>
       <c r="H123" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I123" s="24" t="s">
         <v>40</v>
       </c>
       <c r="J123" s="21" t="s">
-        <v>645</v>
+        <v>303</v>
       </c>
       <c r="K123" s="24" t="s">
         <v>33</v>
@@ -10056,39 +10198,39 @@
       </c>
       <c r="M123" s="25" t="n">
         <f aca="false">H123*(1-L123)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N123" s="24"/>
       <c r="O123" s="21"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="24" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E124" s="21" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="G124" s="21"/>
       <c r="H124" s="25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I124" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J124" s="21" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K124" s="24" t="s">
         <v>33</v>
@@ -10098,39 +10240,39 @@
       </c>
       <c r="M124" s="25" t="n">
         <f aca="false">H124*(1-L124)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N124" s="24"/>
       <c r="O124" s="21"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="24" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E125" s="21" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G125" s="21"/>
       <c r="H125" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I125" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J125" s="21" t="s">
-        <v>653</v>
+        <v>334</v>
       </c>
       <c r="K125" s="24" t="s">
         <v>33</v>
@@ -10140,38 +10282,40 @@
       </c>
       <c r="M125" s="25" t="n">
         <f aca="false">H125*(1-L125)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N125" s="24"/>
       <c r="O125" s="21"/>
     </row>
-    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="24" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>179</v>
+        <v>344</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E126" s="21" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="G126" s="21"/>
       <c r="H126" s="25" t="n">
         <v>3</v>
       </c>
       <c r="I126" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="J126" s="21"/>
+        <v>42</v>
+      </c>
+      <c r="J126" s="21" t="s">
+        <v>660</v>
+      </c>
       <c r="K126" s="24" t="s">
         <v>33</v>
       </c>
@@ -10183,35 +10327,33 @@
         <v>3</v>
       </c>
       <c r="N126" s="24"/>
-      <c r="O126" s="21" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O126" s="21"/>
+    </row>
+    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="24" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E127" s="21" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G127" s="21"/>
       <c r="H127" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I127" s="24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J127" s="21" t="s">
         <v>653</v>
@@ -10224,39 +10366,41 @@
       </c>
       <c r="M127" s="25" t="n">
         <f aca="false">H127*(1-L127)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N127" s="24"/>
-      <c r="O127" s="21"/>
+      <c r="O127" s="21" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="24" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B128" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E128" s="21" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="F128" s="24" t="s">
         <v>179</v>
       </c>
       <c r="G128" s="21"/>
       <c r="H128" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I128" s="24" t="s">
         <v>38</v>
       </c>
       <c r="J128" s="21" t="s">
-        <v>427</v>
+        <v>668</v>
       </c>
       <c r="K128" s="24" t="s">
         <v>33</v>
@@ -10266,39 +10410,39 @@
       </c>
       <c r="M128" s="25" t="n">
         <f aca="false">H128*(1-L128)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N128" s="24"/>
       <c r="O128" s="21"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="24" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B129" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E129" s="21" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>426</v>
+        <v>188</v>
       </c>
       <c r="G129" s="21"/>
       <c r="H129" s="25" t="n">
         <v>4</v>
       </c>
       <c r="I129" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J129" s="21" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
       <c r="K129" s="24" t="s">
         <v>33</v>
@@ -10313,26 +10457,278 @@
       <c r="N129" s="24"/>
       <c r="O129" s="21"/>
     </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="24" t="s">
+        <v>673</v>
+      </c>
+      <c r="B130" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D130" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="E130" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="F130" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="G130" s="21"/>
+      <c r="H130" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J130" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="K130" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="25" t="n">
+        <f aca="false">H130*(1-L130)</f>
+        <v>3</v>
+      </c>
+      <c r="N130" s="24"/>
+      <c r="O130" s="21"/>
+    </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D131" s="16" t="s">
-        <v>667</v>
-      </c>
-      <c r="H131" s="27" t="n">
-        <f aca="false">SUM(H5:H129)</f>
-        <v>441.5</v>
-      </c>
-      <c r="M131" s="27" t="n">
-        <f aca="false">SUM(M5:M129)</f>
-        <v>420.65</v>
+      <c r="A131" s="24" t="s">
+        <v>677</v>
+      </c>
+      <c r="B131" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D131" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E131" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="F131" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="G131" s="21"/>
+      <c r="H131" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I131" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J131" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="K131" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L131" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="25" t="n">
+        <f aca="false">H131*(1-L131)</f>
+        <v>5</v>
+      </c>
+      <c r="N131" s="24"/>
+      <c r="O131" s="21"/>
+    </row>
+    <row r="132" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="24" t="s">
+        <v>681</v>
+      </c>
+      <c r="B132" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D132" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="E132" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="F132" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="G132" s="21"/>
+      <c r="H132" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I132" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J132" s="21"/>
+      <c r="K132" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="25" t="n">
+        <f aca="false">H132*(1-L132)</f>
+        <v>3</v>
+      </c>
+      <c r="N132" s="24"/>
+      <c r="O132" s="21" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="24" t="s">
+        <v>685</v>
+      </c>
+      <c r="B133" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D133" s="21" t="s">
+        <v>686</v>
+      </c>
+      <c r="E133" s="21" t="s">
+        <v>687</v>
+      </c>
+      <c r="F133" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="G133" s="21"/>
+      <c r="H133" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I133" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J133" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="K133" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L133" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="25" t="n">
+        <f aca="false">H133*(1-L133)</f>
+        <v>4</v>
+      </c>
+      <c r="N133" s="24"/>
+      <c r="O133" s="21"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="24" t="s">
+        <v>688</v>
+      </c>
+      <c r="B134" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C134" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D134" s="21" t="s">
+        <v>689</v>
+      </c>
+      <c r="E134" s="21" t="s">
+        <v>690</v>
+      </c>
+      <c r="F134" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="G134" s="21"/>
+      <c r="H134" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J134" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="K134" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L134" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="25" t="n">
+        <f aca="false">H134*(1-L134)</f>
+        <v>3</v>
+      </c>
+      <c r="N134" s="24"/>
+      <c r="O134" s="21"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="24" t="s">
+        <v>691</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="D135" s="21" t="s">
+        <v>692</v>
+      </c>
+      <c r="E135" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="F135" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="G135" s="21"/>
+      <c r="H135" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I135" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J135" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="K135" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="25" t="n">
+        <f aca="false">H135*(1-L135)</f>
+        <v>4</v>
+      </c>
+      <c r="N135" s="24"/>
+      <c r="O135" s="21"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D137" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="H137" s="27" t="n">
+        <f aca="false">SUM(H5:H135)</f>
+        <v>454.5</v>
+      </c>
+      <c r="M137" s="27" t="n">
+        <f aca="false">SUM(M5:M135)</f>
+        <v>409.05</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O129"/>
+  <autoFilter ref="A4:O135"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5:K129">
+  <conditionalFormatting sqref="K5:K135">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"Đã xong"</formula>
     </cfRule>
@@ -10346,7 +10742,7 @@
       <formula>"Chưa bắt đầu"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L129">
+  <conditionalFormatting sqref="L5:L135">
     <cfRule type="dataBar" priority="6">
       <dataBar showValue="1" minLength="10" maxLength="90">
         <cfvo type="num" val="0"/>
@@ -10355,22 +10751,22 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E6ABD13B-60D3-45A0-B1B3-5DA3F8417C30}</x14:id>
+          <x14:id>{4022522D-705D-458F-AE9A-38442D41B535}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I129">
+  <conditionalFormatting sqref="I5:I135">
     <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>"P0-Bắt buộc"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K129" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K135" type="list">
       <formula1>Lists!$A$2:$A$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I129" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I135" type="list">
       <formula1>Lists!$B$2:$B$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10387,7 +10783,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E6ABD13B-60D3-45A0-B1B3-5DA3F8417C30}">
+          <x14:cfRule type="dataBar" id="{4022522D-705D-458F-AE9A-38442D41B535}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10399,7 +10795,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L5:L129</xm:sqref>
+          <xm:sqref>L5:L135</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -10470,7 +10866,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>73</v>
@@ -10484,7 +10880,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>74</v>
@@ -10542,7 +10938,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10555,7 +10951,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10568,31 +10964,31 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>168</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>673</v>
+        <v>700</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10600,10 +10996,10 @@
         <v>179</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>8</v>
@@ -10616,15 +11012,15 @@
         <v>5.6</v>
       </c>
       <c r="G5" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$F$5:$F$129,$A5)</f>
-        <v>41.35</v>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$F$5:$F$135,$A5)</f>
+        <v>39.75</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">IFERROR(ROUND(G5/F5,1),0)</f>
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>680</v>
+        <v>707</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10632,10 +11028,10 @@
         <v>188</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>681</v>
+        <v>708</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>682</v>
+        <v>709</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>8</v>
@@ -10648,24 +11044,24 @@
         <v>7.2</v>
       </c>
       <c r="G6" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$F$5:$F$129,$A6)</f>
-        <v>161.3</v>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$F$5:$F$135,$A6)</f>
+        <v>151.3</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IFERROR(ROUND(G6/F6,1),0)</f>
-        <v>22.4</v>
+        <v>21</v>
       </c>
       <c r="I6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>8</v>
@@ -10678,7 +11074,7 @@
         <v>7.2</v>
       </c>
       <c r="G7" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$F$5:$F$129,$A7)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$F$5:$F$135,$A7)</f>
         <v>104</v>
       </c>
       <c r="H7" s="10" t="n">
@@ -10686,18 +11082,18 @@
         <v>14.4</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>687</v>
+        <v>714</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>8</v>
@@ -10710,7 +11106,7 @@
         <v>7.2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <f aca="false">SUMIFS(Backlog!$M$5:$M$129,Backlog!$F$5:$F$129,$A8)</f>
+        <f aca="false">SUMIFS(Backlog!$M$5:$M$135,Backlog!$F$5:$F$135,$A8)</f>
         <v>114</v>
       </c>
       <c r="H8" s="10" t="n">
@@ -10718,13 +11114,13 @@
         <v>15.8</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="13"/>
@@ -10735,19 +11131,19 @@
       </c>
       <c r="G9" s="14" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>420.65</v>
+        <v>409.05</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
@@ -10760,7 +11156,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -10773,7 +11169,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -10786,7 +11182,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -10799,7 +11195,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -10851,7 +11247,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>696</v>
+        <v>723</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10860,7 +11256,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10872,391 +11268,391 @@
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>155</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>704</v>
+        <v>731</v>
       </c>
       <c r="E5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>705</v>
+        <v>732</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>155</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>707</v>
+        <v>734</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>709</v>
+        <v>736</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="E8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>722</v>
+        <v>749</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>723</v>
+        <v>750</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>724</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>725</v>
+        <v>752</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="E11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>739</v>
+        <v>766</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>740</v>
+        <v>767</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>741</v>
+        <v>768</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>742</v>
+        <v>769</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="E15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>744</v>
+        <v>771</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>745</v>
+        <v>772</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="E16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>748</v>
+        <v>775</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>749</v>
+        <v>776</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>751</v>
+        <v>778</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>752</v>
+        <v>779</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="E18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>757</v>
+        <v>784</v>
       </c>
       <c r="E19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>763</v>
+        <v>790</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>766</v>
+        <v>793</v>
       </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="E22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>771</v>
+        <v>798</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="E24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="30" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="C25" s="30" t="s">
         <v>151</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>779</v>
+        <v>806</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>782</v>
+        <v>809</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="E26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="30" t="s">
-        <v>785</v>
+        <v>812</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>786</v>
+        <v>813</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>787</v>
+        <v>814</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>788</v>
+        <v>815</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>789</v>
+        <v>816</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>790</v>
+        <v>817</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -11265,7 +11661,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
-        <v>791</v>
+        <v>818</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -11274,7 +11670,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>792</v>
+        <v>819</v>
       </c>
       <c r="B33" s="29"/>
       <c r="C33" s="29"/>
@@ -11283,7 +11679,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
@@ -11292,7 +11688,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
@@ -11301,7 +11697,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
@@ -11347,7 +11743,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11358,7 +11754,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11369,45 +11765,45 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>798</v>
+        <v>825</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>801</v>
+        <v>828</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="G5" s="22" t="s">
         <v>179</v>
@@ -11415,22 +11811,22 @@
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>812</v>
+        <v>839</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="G6" s="22" t="s">
         <v>179</v>
@@ -11438,45 +11834,45 @@
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>817</v>
+        <v>844</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>818</v>
+        <v>845</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>821</v>
+        <v>848</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>179</v>
@@ -11484,22 +11880,22 @@
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>824</v>
+        <v>851</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>188</v>
@@ -11507,22 +11903,22 @@
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>179</v>
@@ -11530,22 +11926,22 @@
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>832</v>
+        <v>859</v>
       </c>
       <c r="B11" s="21" t="s">
+        <v>860</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>833</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>829</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>806</v>
-      </c>
       <c r="E11" s="21" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>179</v>
@@ -11553,45 +11949,45 @@
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>841</v>
+        <v>868</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>179</v>
@@ -11630,7 +12026,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11642,7 +12038,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11651,7 +12047,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11660,221 +12056,340 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>850</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>859</v>
+        <v>886</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>861</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>868</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>869</v>
+        <v>896</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>870</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="s">
         <v>878</v>
       </c>
-      <c r="B18" s="36" t="s">
-        <v>879</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>880</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>882</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>883</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>884</v>
+      <c r="B13" s="34" t="s">
+        <v>903</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>889</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>904</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>878</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>903</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>889</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>906</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="s">
+        <v>878</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>903</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>908</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="s">
+        <v>878</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>903</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>911</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>912</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="s">
+        <v>878</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>903</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>914</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="s">
+        <v>878</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>903</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>916</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="s">
+        <v>878</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>918</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>919</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>886</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>887</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>888</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>890</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>891</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>892</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>893</v>
+        <v>920</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="35" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="36" t="s">
+        <v>924</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>925</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>926</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>928</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>929</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>930</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
+        <v>932</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>933</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>934</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
+        <v>936</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>937</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>938</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>939</v>
       </c>
     </row>
   </sheetData>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -2252,20 +2252,20 @@
       </c>
       <c r="B17" s="60" t="inlineStr">
         <is>
-          <t>Chưa có</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="C17" s="61" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="D17" s="59" t="inlineStr">
         <is>
-          <t>Chỉ có UserRole enum 3 giá trị, không có permission/vai trò/audit</t>
+          <t>domains/iam: 12 vai trò, quyền domain:action:scope, đăng nhập 2FA, maker-checker, che PII, API vận hành cho Console</t>
         </is>
       </c>
       <c r="E17" s="59" t="inlineStr">
         <is>
-          <t>Toàn bộ P1</t>
+          <t>Thiếu: giao diện Console (P1-12…P1-19, phần frontend)</t>
         </is>
       </c>
     </row>
@@ -2352,20 +2352,20 @@
       </c>
       <c r="B21" s="60" t="inlineStr">
         <is>
-          <t>Chưa có</t>
+          <t>Một nửa</t>
         </is>
       </c>
       <c r="C21" s="61" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D21" s="59" t="inlineStr">
         <is>
-          <t>Không tồn tại (backend đã có sẵn vài API /admin/*)</t>
+          <t>Backend đã đủ API: IAM, audit, fleet, duyệt tài xế, tra cứu chuyến, duyệt chi tiền</t>
         </is>
       </c>
       <c r="E21" s="59" t="inlineStr">
         <is>
-          <t>P1 + P2 + P5</t>
+          <t>Thiếu toàn bộ phần giao diện (P1-12…P1-19)</t>
         </is>
       </c>
     </row>
@@ -2456,11 +2456,11 @@
         </is>
       </c>
       <c r="C25" s="61" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D25" s="59" t="inlineStr">
         <is>
-          <t>192 test backend xanh, độ phủ 81,5%; smoke E2E 22 bước và rà soát ngang 62 lời gọi API chạy trên server thật</t>
+          <t>243 test backend xanh, độ phủ 82%; smoke 22 bước và audit 62 lời gọi trên server thật</t>
         </is>
       </c>
       <c r="E25" s="59" t="inlineStr">
@@ -3612,11 +3612,11 @@
       </c>
       <c r="K20" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L20" s="64" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M20" s="63">
         <f>H20*(1-L20)</f>
@@ -3625,7 +3625,7 @@
       <c r="N20" s="62" t="n"/>
       <c r="O20" s="59" t="inlineStr">
         <is>
-          <t>03/09: xong phần mã — Prometheus /metrics (nhãn path theo template route, khoá bằng METRICS_TOKEN), OTel trace tuỳ chọn, Sentry theo DSN, X-Request-ID xuyên log/audit. 9 test QA-MET. Còn: dựng collector + alert Slack trên staging (chờ P0-10).</t>
+          <t>03/09 XONG: Prometheus /metrics (nhãn theo template route, khoá bằng METRICS_TOKEN), OTel trace tuỳ chọn, Sentry theo DSN, X-Request-ID xuyên log/audit. Alert Slack nối khi có staging.</t>
         </is>
       </c>
     </row>
@@ -4408,11 +4408,11 @@
       </c>
       <c r="K33" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L33" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="63">
         <f>H33*(1-L33)</f>
@@ -4421,7 +4421,7 @@
       <c r="N33" s="62" t="n"/>
       <c r="O33" s="59" t="inlineStr">
         <is>
-          <t>Hoàn toàn chưa có — hiện chỉ có UserRole enum 3 giá trị (rider/driver/admin)</t>
+          <t>03/09 XONG: domains/iam + migration 0004 (staff_users, roles, permissions, role_permissions, staff_roles). Seed 12 vai trò đúng ma trận phân định §2.3, chạy lại không nhân đôi.</t>
         </is>
       </c>
     </row>
@@ -4472,18 +4472,22 @@
       </c>
       <c r="K34" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L34" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="63">
         <f>H34*(1-L34)</f>
         <v/>
       </c>
       <c r="N34" s="62" t="n"/>
-      <c r="O34" s="59" t="n"/>
+      <c r="O34" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: email + mật khẩu + TOTP bắt buộc, phiên 8 giờ, khoá sau 5 lần sai (15 phút), admin gỡ khoá sớm được. Xoay vòng refresh token. Ghim bcrypt==4.2.1 vì passlib vỡ với bcrypt 5.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="38">
       <c r="A35" s="62" t="inlineStr">
@@ -4532,18 +4536,22 @@
       </c>
       <c r="K35" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L35" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="63">
         <f>H35*(1-L35)</f>
         <v/>
       </c>
       <c r="N35" s="62" t="n"/>
-      <c r="O35" s="59" t="n"/>
+      <c r="O35" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: require_permission('domain:action:scope') trả 403 kèm đúng mã quyền còn thiếu.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="38">
       <c r="A36" s="62" t="inlineStr">
@@ -4592,18 +4600,22 @@
       </c>
       <c r="K36" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L36" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="63">
         <f>H36*(1-L36)</f>
         <v/>
       </c>
       <c r="N36" s="62" t="n"/>
-      <c r="O36" s="59" t="n"/>
+      <c r="O36" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: /ops/staff CRUD + gán vai trò + vô hiệu hoá (không xoá) + gỡ khoá. Bí mật TOTP chỉ trả về một lần lúc tạo.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="38">
       <c r="A37" s="62" t="inlineStr">
@@ -4652,18 +4664,22 @@
       </c>
       <c r="K37" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L37" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="63">
         <f>H37*(1-L37)</f>
         <v/>
       </c>
       <c r="N37" s="62" t="n"/>
-      <c r="O37" s="59" t="n"/>
+      <c r="O37" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: GET /ops/audit-logs lọc theo người/nhân sự/đối tượng/thời gian, phân trang con trỏ.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22.35" customHeight="1" s="38">
       <c r="A38" s="62" t="inlineStr">
@@ -4712,11 +4728,11 @@
       </c>
       <c r="K38" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L38" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="63">
         <f>H38*(1-L38)</f>
@@ -4725,7 +4741,7 @@
       <c r="N38" s="62" t="n"/>
       <c r="O38" s="59" t="inlineStr">
         <is>
-          <t>core/security.py đã có mã hoá CCCD at-rest, chưa có lớp che khi hiển thị</t>
+          <t>03/09 XONG: core/pii che SĐT/CCCD/email/tên; GET /ops/users/{id} trả bản đã che; POST /ops/users/{id}/reveal-pii cần quyền pii:full:read + lý do ≥10 ký tự, ghi vào audit_logs.reason.</t>
         </is>
       </c>
     </row>
@@ -4776,18 +4792,22 @@
       </c>
       <c r="K39" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L39" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="63">
         <f>H39*(1-L39)</f>
         <v/>
       </c>
       <c r="N39" s="62" t="n"/>
-      <c r="O39" s="59" t="n"/>
+      <c r="O39" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: approval_requests + migration 0005, 5 loại đề nghị. Người tạo không tự duyệt (kể cả super_admin), quá hạn 72h tự đóng bằng job Celery mỗi 30 phút.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="38">
       <c r="A40" s="62" t="inlineStr">
@@ -4836,11 +4856,11 @@
       </c>
       <c r="K40" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L40" s="64" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M40" s="63">
         <f>H40*(1-L40)</f>
@@ -4849,7 +4869,7 @@
       <c r="N40" s="62" t="n"/>
       <c r="O40" s="59" t="inlineStr">
         <is>
-          <t>Hiện router gom theo tài nguyên, lẫn vai trò trong cùng file</t>
+          <t>03/09: bề mặt /ops đã tách thật (iam, users, approvals, fleet/drivers/trips). Còn: /rider, /driver, /partner, /public vẫn dùng đường dẫn cũ.</t>
         </is>
       </c>
     </row>
@@ -4900,11 +4920,11 @@
       </c>
       <c r="K41" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L41" s="64" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M41" s="63">
         <f>H41*(1-L41)</f>
@@ -4913,7 +4933,7 @@
       <c r="N41" s="62" t="n"/>
       <c r="O41" s="59" t="inlineStr">
         <is>
-          <t>Redis GEO đã có sẵn — tái dùng được</t>
+          <t>03/09: GET /ops/fleet trả ảnh chụp toàn đội (online, đang chạy chuyến), không kèm PII. Còn: WS ops.fleet_update gom 3s/lần — chờ WS gateway đa topic ở P2.</t>
         </is>
       </c>
     </row>
@@ -4964,18 +4984,22 @@
       </c>
       <c r="K42" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L42" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="63">
         <f>H42*(1-L42)</f>
         <v/>
       </c>
       <c r="N42" s="62" t="n"/>
-      <c r="O42" s="59" t="n"/>
+      <c r="O42" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: /ops/drivers lọc theo trạng thái duyệt, duyệt/từ chối có lý do + thông báo cho tài xế, khoá/mở tài khoản (khoá là xoá luôn QR đang sống). Migration 0006.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="38">
       <c r="A43" s="62" t="inlineStr">
@@ -5024,11 +5048,11 @@
       </c>
       <c r="K43" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L43" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="63">
         <f>H43*(1-L43)</f>
@@ -5037,7 +5061,7 @@
       <c r="N43" s="62" t="n"/>
       <c r="O43" s="59" t="inlineStr">
         <is>
-          <t>gps-history đã có ở phía rider, cần bản cho ops</t>
+          <t>03/09 XONG: GET /ops/trips lọc theo trạng thái/tài xế/khách/thời gian + phân trang con trỏ, chi tiết chuyến, tua lại lộ trình GPS, số liệu đầu trang.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -2352,20 +2352,20 @@
       </c>
       <c r="B21" s="60" t="inlineStr">
         <is>
-          <t>Một nửa</t>
+          <t>Gần xong</t>
         </is>
       </c>
       <c r="C21" s="61" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D21" s="59" t="inlineStr">
         <is>
-          <t>Backend đã đủ API: IAM, audit, fleet, duyệt tài xế, tra cứu chuyến, duyệt chi tiền</t>
+          <t>apps/ops-console chạy được: đăng nhập 2FA, Live Ops, duyệt tài xế, tra cứu chuyến + lộ trình, IAM, hàng đợi phê duyệt, nhật ký thao tác</t>
         </is>
       </c>
       <c r="E21" s="59" t="inlineStr">
         <is>
-          <t>Thiếu toàn bộ phần giao diện (P1-12…P1-19)</t>
+          <t>Thiếu: bản đồ thật, đẩy real-time, sửa quyền vai trò từ giao diện</t>
         </is>
       </c>
     </row>
@@ -5112,18 +5112,22 @@
       </c>
       <c r="K44" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L44" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="63">
         <f>H44*(1-L44)</f>
         <v/>
       </c>
       <c r="N44" s="62" t="n"/>
-      <c r="O44" s="59" t="n"/>
+      <c r="O44" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: apps/ops-console — Vite + TS + react-router, tầng auth tự làm mới token (một lần refresh tại một thời điểm), layout + menu dựng theo quyền, xử lý 401/403.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="38">
       <c r="A45" s="62" t="inlineStr">
@@ -5172,18 +5176,22 @@
       </c>
       <c r="K45" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L45" s="64" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M45" s="63">
         <f>H45*(1-L45)</f>
         <v/>
       </c>
       <c r="N45" s="62" t="n"/>
-      <c r="O45" s="59" t="n"/>
+      <c r="O45" s="59" t="inlineStr">
+        <is>
+          <t>03/09: màn hình đăng nhập email + mật khẩu + TOTP, thông điệp lỗi không lộ email nào có thật. Còn: ghi nhớ thiết bị 30 ngày.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="22.35" customHeight="1" s="38">
       <c r="A46" s="62" t="inlineStr">
@@ -5232,18 +5240,22 @@
       </c>
       <c r="K46" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L46" s="64" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M46" s="63">
         <f>H46*(1-L46)</f>
         <v/>
       </c>
       <c r="N46" s="62" t="n"/>
-      <c r="O46" s="59" t="n"/>
+      <c r="O46" s="59" t="inlineStr">
+        <is>
+          <t>03/09: src/components/ui.tsx có Card/Table/Badge/Button/Empty dùng chung trong Console. Còn: tách ra packages/ui + Storybook khi Partner Portal cần dùng lại.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="22.35" customHeight="1" s="38">
       <c r="A47" s="62" t="inlineStr">
@@ -5292,18 +5304,22 @@
       </c>
       <c r="K47" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L47" s="64" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M47" s="63">
         <f>H47*(1-L47)</f>
         <v/>
       </c>
       <c r="N47" s="62" t="n"/>
-      <c r="O47" s="59" t="n"/>
+      <c r="O47" s="59" t="inlineStr">
+        <is>
+          <t>03/09: màn hình nhân sự (tạo, gán vai trò, vô hiệu hoá, gỡ khoá), ma trận vai trò, nhật ký thao tác có lọc và phân trang. Còn: sửa quyền của vai trò từ giao diện (cần API iam:role:write).</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="38">
       <c r="A48" s="62" t="inlineStr">
@@ -5352,18 +5368,22 @@
       </c>
       <c r="K48" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L48" s="64" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M48" s="63">
         <f>H48*(1-L48)</f>
         <v/>
       </c>
       <c r="N48" s="62" t="n"/>
-      <c r="O48" s="59" t="n"/>
+      <c r="O48" s="59" t="inlineStr">
+        <is>
+          <t>03/09: màn hình Live Ops hiện toàn đội, làm mới mỗi 5 giây, có lọc và số liệu tổng quan. Còn: bản đồ thật (Goong/Mapbox) và đẩy real-time qua WS.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="38">
       <c r="A49" s="62" t="inlineStr">
@@ -5412,18 +5432,22 @@
       </c>
       <c r="K49" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L49" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="63">
         <f>H49*(1-L49)</f>
         <v/>
       </c>
       <c r="N49" s="62" t="n"/>
-      <c r="O49" s="59" t="n"/>
+      <c r="O49" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: duyệt/từ chối hồ sơ có lý do, khoá/mở tài khoản, xem PII đầy đủ kèm lý do — duyệt được một hồ sơ từ đầu đến cuối không cần đụng DB.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="38">
       <c r="A50" s="62" t="inlineStr">
@@ -5472,18 +5496,22 @@
       </c>
       <c r="K50" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L50" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="63">
         <f>H50*(1-L50)</f>
         <v/>
       </c>
       <c r="N50" s="62" t="n"/>
-      <c r="O50" s="59" t="n"/>
+      <c r="O50" s="59" t="inlineStr">
+        <is>
+          <t>03/09 XONG: danh sách chuyến có lọc + tải thêm theo con trỏ, xem lại lộ trình GPS của chuyến.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="22.35" customHeight="1" s="38">
       <c r="A51" s="62" t="inlineStr">
@@ -5532,18 +5560,22 @@
       </c>
       <c r="K51" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L51" s="64" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M51" s="63">
         <f>H51*(1-L51)</f>
         <v/>
       </c>
       <c r="N51" s="62" t="n"/>
-      <c r="O51" s="59" t="n"/>
+      <c r="O51" s="59" t="inlineStr">
+        <is>
+          <t>03/09: 27 test IAM + 11 test API vận hành phủ phân quyền theo vai trò ở tầng backend. Còn: test giao diện Console.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="22.35" customHeight="1" s="38">
       <c r="A52" s="62" t="inlineStr">

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="L11" s="64" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="M11" s="63">
         <f>H11*(1-L11)</f>
@@ -3073,7 +3073,7 @@
       <c r="N11" s="62" t="n"/>
       <c r="O11" s="59" t="inlineStr">
         <is>
-          <t>03/09: .github/workflows/ci.yml 4 job (backend, migration-check, api-contract, frontend) đều xanh. Còn: bật branch protection trên GitHub để PR đỏ không merge được — thao tác trên giao diện.</t>
+          <t>03/09: CI 4 job. Job Frontend từng đỏ ngay bước cài pnpm (khai version trùng với packageManager) — đã sửa. Còn: bật branch protection trên giao diện GitHub.</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       <c r="N12" s="62" t="n"/>
       <c r="O12" s="59" t="inlineStr">
         <is>
-          <t>03/09 XONG: job migration-check chạy alembic upgrade head + alembic check trên container postgis:16-3.4. Sửa model mà quên migration là CI đỏ ngay.</t>
+          <t>03/09 XONG: alembic upgrade head + alembic check chạy sạch trên Postgres 16 + PostGIS. Sửa lỗi enum tạo hai lần ở 0003/0005/0006 và gộp ràng buộc users.phone (0007). Đã kiểm chứng cả downgrade base rồi upgrade lại.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -2684,11 +2684,11 @@
       <c r="J5" s="59" t="n"/>
       <c r="K5" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L5" s="64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M5" s="63">
         <f>H5*(1-L5)</f>
@@ -2697,7 +2697,7 @@
       <c r="N5" s="62" t="n"/>
       <c r="O5" s="59" t="inlineStr">
         <is>
-          <t>03/09: đã chuyển thành services/_deprecated-api-v0 kèm DEPRECATED.md. Điều kiện xoá ĐÃ ĐẠT (P4-12 xong, app khách không còn phụ thuộc). Chỉ còn thao tác xoá thư mục.</t>
+          <t>03/09 XONG: đã xoá hẳn services/_deprecated-api-v0 khỏi repo sau khi app khách chuyển xong sang API mới (P4-12). Gỡ luôn các chỗ tài liệu còn trỏ tới nó.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -2152,20 +2152,20 @@
       </c>
       <c r="B13" s="60" t="inlineStr">
         <is>
-          <t>Một nửa</t>
+          <t>Gần xong</t>
         </is>
       </c>
       <c r="C13" s="61" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D13" s="59" t="inlineStr">
         <is>
-          <t>connection_manager + Redis pub/sub + events cơ bản</t>
+          <t>connection_manager + Redis pub/sub + kênh riêng cho Console (gom 3s/lần)</t>
         </is>
       </c>
       <c r="E13" s="59" t="inlineStr">
         <is>
-          <t>Cần mở rộng đa topic cho chat và ops</t>
+          <t>Thiếu: đa topic cho chat (P2)</t>
         </is>
       </c>
     </row>
@@ -2352,20 +2352,20 @@
       </c>
       <c r="B21" s="60" t="inlineStr">
         <is>
-          <t>Gần xong</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="C21" s="61" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D21" s="59" t="inlineStr">
         <is>
-          <t>apps/ops-console chạy được: đăng nhập 2FA, Live Ops, duyệt tài xế, tra cứu chuyến + lộ trình, IAM, hàng đợi phê duyệt, nhật ký thao tác</t>
+          <t>Đăng nhập 2FA + nhớ máy, bản đồ Live Ops real-time, duyệt tài xế, tra cứu chuyến + lộ trình, IAM + sửa quyền vai trò, hàng đợi phê duyệt, nhật ký</t>
         </is>
       </c>
       <c r="E21" s="59" t="inlineStr">
         <is>
-          <t>Thiếu: bản đồ thật, đẩy real-time, sửa quyền vai trò từ giao diện</t>
+          <t>Bổ sung theo nhu cầu vận hành thật</t>
         </is>
       </c>
     </row>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="K40" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L40" s="64" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M40" s="63">
         <f>H40*(1-L40)</f>
@@ -4869,7 +4869,7 @@
       <c r="N40" s="62" t="n"/>
       <c r="O40" s="59" t="inlineStr">
         <is>
-          <t>03/09: bề mặt /ops đã tách thật (iam, users, approvals, fleet/drivers/trips). Còn: /rider, /driver, /partner, /public vẫn dùng đường dẫn cũ.</t>
+          <t>03/09 XONG: app/api dựng 5 nhóm rider/driver/ops/partner/public từ chính route đã có, không viết lại handler. Đường dẫn cũ vẫn chạy, đánh dấu deprecated. Có test bắt buộc mọi route phải khai nhóm. Nhóm partner dựng sẵn, endpoint đến P6 mới có.</t>
         </is>
       </c>
     </row>
@@ -4920,11 +4920,11 @@
       </c>
       <c r="K41" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L41" s="64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M41" s="63">
         <f>H41*(1-L41)</f>
@@ -4933,7 +4933,7 @@
       <c r="N41" s="62" t="n"/>
       <c r="O41" s="59" t="inlineStr">
         <is>
-          <t>03/09: GET /ops/fleet trả ảnh chụp toàn đội (online, đang chạy chuyến), không kèm PII. Còn: WS ops.fleet_update gom 3s/lần — chờ WS gateway đa topic ở P2.</t>
+          <t>03/09 XONG: /ws/ops/fleet đẩy ảnh chụp mỗi 3 giây, kiểm quyền ops:fleet:read, hết người xem thì dừng vòng lặp. Console tự lùi về hỏi lại 5 giây/lần nếu WS không mở được.</t>
         </is>
       </c>
     </row>
@@ -5176,11 +5176,11 @@
       </c>
       <c r="K45" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L45" s="64" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M45" s="63">
         <f>H45*(1-L45)</f>
@@ -5189,7 +5189,7 @@
       <c r="N45" s="62" t="n"/>
       <c r="O45" s="59" t="inlineStr">
         <is>
-          <t>03/09: màn hình đăng nhập email + mật khẩu + TOTP, thông điệp lỗi không lộ email nào có thật. Còn: ghi nhớ thiết bị 30 ngày.</t>
+          <t>03/09 XONG: nhớ máy 30 ngày (bảng staff_trusted_devices, chỉ lưu hash). Mật khẩu không bao giờ bị bỏ qua; gỡ được ngay khi mất máy, tự gỡ hoặc quản trị gỡ hộ.</t>
         </is>
       </c>
     </row>
@@ -5240,11 +5240,11 @@
       </c>
       <c r="K46" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L46" s="64" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="M46" s="63">
         <f>H46*(1-L46)</f>
@@ -5253,7 +5253,7 @@
       <c r="N46" s="62" t="n"/>
       <c r="O46" s="59" t="inlineStr">
         <is>
-          <t>03/09: src/components/ui.tsx có Card/Table/Badge/Button/Empty dùng chung trong Console. Còn: tách ra packages/ui + Storybook khi Partner Portal cần dùng lại.</t>
+          <t>03/09 XONG: packages/ui tách khỏi Console (Card/Table/Badge/Button/Empty/ErrorText), chỉ JSX + class nên Partner Portal nạp bảng màu riêng vẫn dùng lại được. Storybook chạy và build ra.</t>
         </is>
       </c>
     </row>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="K47" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L47" s="64" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M47" s="63">
         <f>H47*(1-L47)</f>
@@ -5317,7 +5317,7 @@
       <c r="N47" s="62" t="n"/>
       <c r="O47" s="59" t="inlineStr">
         <is>
-          <t>03/09: màn hình nhân sự (tạo, gán vai trò, vô hiệu hoá, gỡ khoá), ma trận vai trò, nhật ký thao tác có lọc và phân trang. Còn: sửa quyền của vai trò từ giao diện (cần API iam:role:write).</t>
+          <t>03/09 XONG: PUT /ops/roles/{code}/permissions + màn hình tích chọn quyền. Chặn sửa super_admin và chặn gán quyền vạn năng cho vai trò thường.</t>
         </is>
       </c>
     </row>
@@ -5368,11 +5368,11 @@
       </c>
       <c r="K48" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L48" s="64" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M48" s="63">
         <f>H48*(1-L48)</f>
@@ -5381,7 +5381,7 @@
       <c r="N48" s="62" t="n"/>
       <c r="O48" s="59" t="inlineStr">
         <is>
-          <t>03/09: màn hình Live Ops hiện toàn đội, làm mới mỗi 5 giây, có lọc và số liệu tổng quan. Còn: bản đồ thật (Goong/Mapbox) và đẩy real-time qua WS.</t>
+          <t>03/09 XONG: bản đồ Leaflet + OpenStreetMap, marker di chuyển tại chỗ (không vẽ lại nên không nhấp nháy mỗi 3 giây), popup xem chi tiết. Đổi sang Goong chỉ là đổi URL tile.</t>
         </is>
       </c>
     </row>
@@ -5560,11 +5560,11 @@
       </c>
       <c r="K51" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L51" s="64" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M51" s="63">
         <f>H51*(1-L51)</f>
@@ -5573,7 +5573,7 @@
       <c r="N51" s="62" t="n"/>
       <c r="O51" s="59" t="inlineStr">
         <is>
-          <t>03/09: 27 test IAM + 11 test API vận hành phủ phân quyền theo vai trò ở tầng backend. Còn: test giao diện Console.</t>
+          <t>03/09 XONG: 7 test giao diện (vitest + testing-library) phủ 5 vai trò và luồng đăng nhập nhớ máy; CI chạy pnpm test. Test bắt được lỗi thật: trang trắng khi API trả hình dạng lạ.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -2431,16 +2431,16 @@
         </is>
       </c>
       <c r="C24" s="61" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D24" s="59" t="inlineStr">
         <is>
-          <t>CI 4 job xanh (lint/type/test+ngưỡng độ phủ, alembic check, contract API, build frontend)</t>
+          <t>CI 4 job xanh; secret quản lý bằng SOPS+age có cổng chặn tự động; toàn bộ stack đã chạy thật trên Postgres + Redis + Celery</t>
         </is>
       </c>
       <c r="E24" s="59" t="inlineStr">
         <is>
-          <t>Thiếu: staging, quản lý secret, backup PITR — P0-10/11/18</t>
+          <t>Thiếu: máy chủ staging (P0-10) và backup PITR (P0-18) — cần VPS</t>
         </is>
       </c>
     </row>
@@ -2452,20 +2452,20 @@
       </c>
       <c r="B25" s="60" t="inlineStr">
         <is>
-          <t>Một nửa</t>
+          <t>Gần xong</t>
         </is>
       </c>
       <c r="C25" s="61" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="D25" s="59" t="inlineStr">
         <is>
-          <t>243 test backend xanh, độ phủ 82%; smoke 22 bước và audit 62 lời gọi trên server thật</t>
+          <t>277 test backend + 7 test giao diện Console; smoke 22/22 và audit 76/76 chạy thật trên PostgreSQL</t>
         </is>
       </c>
       <c r="E25" s="59" t="inlineStr">
         <is>
-          <t>Thiếu: test frontend và E2E qua app trên staging</t>
+          <t>Thiếu: E2E qua app trên staging</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       <c r="N11" s="62" t="n"/>
       <c r="O11" s="59" t="inlineStr">
         <is>
-          <t>03/09: CI 4 job. Job Frontend từng đỏ ngay bước cài pnpm (khai version trùng với packageManager) — đã sửa. Còn: bật branch protection trên giao diện GitHub.</t>
+          <t>03/09: CI 5 bước xanh (secret, lint, type, test+độ phủ, money, security) + 3 job khác. Còn: bật branch protection trên giao diện GitHub — thao tác ngoài repo.</t>
         </is>
       </c>
     </row>
@@ -3184,11 +3184,11 @@
       <c r="J13" s="59" t="n"/>
       <c r="K13" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L13" s="64" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M13" s="63">
         <f>H13*(1-L13)</f>
@@ -3197,7 +3197,7 @@
       <c r="N13" s="62" t="n"/>
       <c r="O13" s="59" t="inlineStr">
         <is>
-          <t>03/09: compose đủ 4 dịch vụ (postgres+postgis, redis, app, worker chạy kèm beat -B); docker compose config hợp lệ. Còn: chạy up kiểm chứng trên máy có Docker.</t>
+          <t>03/09 XONG: chạy thật đủ bộ dịch vụ (Postgres 16 + PostGIS, Redis, uvicorn, celery worker kèm beat). /health + /ready xanh, smoke 22/22, audit 76/76. docker compose config hợp lệ; lệnh `docker compose up` chưa chạy được vì môi trường phiên làm việc không có Docker daemon.</t>
         </is>
       </c>
     </row>
@@ -3304,11 +3304,11 @@
       <c r="J15" s="59" t="n"/>
       <c r="K15" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L15" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="63">
         <f>H15*(1-L15)</f>
@@ -3317,7 +3317,7 @@
       <c r="N15" s="62" t="n"/>
       <c r="O15" s="59" t="inlineStr">
         <is>
-          <t>Hiện .env đang bị gitignore đúng, nhưng chưa có cơ chế quản lý khoá production</t>
+          <t>03/09 XONG: SOPS + age. .sops.yaml + make secrets-init/new/edit/decrypt/add-key. scripts/check_secrets.py chặn .env chữ thường, khoá riêng và giá trị trông như secret — chạy trong make check và trong CI. Đã thử toàn bộ vòng mã hoá/giải mã.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -3248,18 +3248,22 @@
       </c>
       <c r="K14" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L14" s="64" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M14" s="63">
         <f>H14*(1-L14)</f>
         <v/>
       </c>
       <c r="N14" s="62" t="n"/>
-      <c r="O14" s="59" t="n"/>
+      <c r="O14" s="59" t="inlineStr">
+        <is>
+          <t>03/09: deploy/ có đủ docker-compose.prod.yml (api + worker + beat riêng + postgres WAL archiving + redis + Caddy TLS tự động), Caddyfile chặn /metrics ra ngoài, README ghi từng lệnh. CÒN LẠI: mua VPS + trỏ tên miền rồi chạy — phần này nằm ngoài repo.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22.35" customHeight="1" s="38">
       <c r="A15" s="62" t="inlineStr">
@@ -3736,11 +3740,11 @@
       </c>
       <c r="K22" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L22" s="64" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M22" s="63">
         <f>H22*(1-L22)</f>
@@ -3749,7 +3753,7 @@
       <c r="N22" s="62" t="n"/>
       <c r="O22" s="59" t="inlineStr">
         <is>
-          <t>Bắt buộc vì có dữ liệu ký quỹ của tài xế</t>
+          <t>03/09: deploy/backup.sh (dump hằng ngày, tự kiểm bằng pg_restore --list, giữ 30 ngày) + restore.sh + WAL archiving cho PITR. ĐÃ CHẠY THẬT: sao lưu rồi khôi phục sang DB khác, đủ 7 user, 7 chuyến, 5 bút toán ký quỹ, 114 dòng audit. CÒN LẠI: cắm vào máy chủ staging và đặt lịch diễn tập khôi phục mỗi quý.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -5628,11 +5628,11 @@
       </c>
       <c r="K52" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L52" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="63">
         <f>H52*(1-L52)</f>
@@ -5641,7 +5641,7 @@
       <c r="N52" s="62" t="n"/>
       <c r="O52" s="59" t="inlineStr">
         <is>
-          <t>Hoàn toàn chưa có — đây là module mới</t>
+          <t>04/09 XONG: migration 0009 tạo conversations / conversation_members / messages / message_attachments + đủ chỉ mục. Chạy sạch cả upgrade lẫn downgrade trên PostgreSQL 16 thật, alembic check không phát sinh thao tác mới.</t>
         </is>
       </c>
     </row>
@@ -5692,18 +5692,22 @@
       </c>
       <c r="K53" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L53" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="63">
         <f>H53*(1-L53)</f>
         <v/>
       </c>
       <c r="N53" s="62" t="n"/>
-      <c r="O53" s="59" t="n"/>
+      <c r="O53" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: send_message() khử trùng theo (conversation_id, client_msg_id) — ràng buộc UNIQUE ở DB, thêm nhánh bắt IntegrityError cho trường hợp hai request vào cùng lúc. Test: gửi lại cùng client_msg_id trả về đúng tin cũ, DB vẫn 1 dòng.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="38">
       <c r="A54" s="62" t="inlineStr">
@@ -5752,18 +5756,22 @@
       </c>
       <c r="K54" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L54" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="63">
         <f>H54*(1-L54)</f>
         <v/>
       </c>
       <c r="N54" s="62" t="n"/>
-      <c r="O54" s="59" t="n"/>
+      <c r="O54" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: list_messages() phân trang con trỏ hai chiều (before/after), sắp theo (created_at, id). created_at sinh ở Python chứ không dùng func.now(): trên Postgres now() trả mốc đầu transaction nên mọi tin cùng transaction sẽ trùng mốc và thứ tự loạn. Test dựng đúng kịch bản mất mạng 5 phút.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="38">
       <c r="A55" s="62" t="inlineStr">
@@ -5812,18 +5820,22 @@
       </c>
       <c r="K55" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L55" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="63">
         <f>H55*(1-L55)</f>
         <v/>
       </c>
       <c r="N55" s="62" t="n"/>
-      <c r="O55" s="59" t="n"/>
+      <c r="O55" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: mark_read() chỉ tiến không lùi (hai thiết bị đọc lệch nhau không làm số chưa đọc nhảy ngược), unread_count không tính tin của chính mình. Có endpoint POST /chat/conversations/{id}/read.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="38">
       <c r="A56" s="62" t="inlineStr">
@@ -5872,18 +5884,22 @@
       </c>
       <c r="K56" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L56" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="63">
         <f>H56*(1-L56)</f>
         <v/>
       </c>
       <c r="N56" s="62" t="n"/>
-      <c r="O56" s="59" t="n"/>
+      <c r="O56" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: chat.typing đi qua WS, KHÔNG lưu DB, chỉ chuyển tiếp cho thành viên còn lại và không dội về người gõ. Có kiểm tư cách thành viên trên kênh WS y như REST — test bảo mật chứng minh người ngoài biết id hội thoại vẫn không phát được tín hiệu. Tự tắt sau 5s là việc của client.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="38">
       <c r="A57" s="62" t="inlineStr">
@@ -5932,11 +5948,11 @@
       </c>
       <c r="K57" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L57" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="63">
         <f>H57*(1-L57)</f>
@@ -5945,7 +5961,7 @@
       <c r="N57" s="62" t="n"/>
       <c r="O57" s="59" t="inlineStr">
         <is>
-          <t>Đây là yêu cầu cốt lõi: chat 3 bên CSKH - tài xế - khách</t>
+          <t>04/09 XONG: agent_join / agent_leave sinh tin hệ thống, cả khách và tài xế đều thấy. Rời hội thoại ghi mốc left_at chứ không xoá dòng — khiếu nại đến sau vài tuần vẫn tra được lúc đó ai đang ở trong cuộc.</t>
         </is>
       </c>
     </row>
@@ -5996,18 +6012,22 @@
       </c>
       <c r="K58" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L58" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="63">
         <f>H58*(1-L58)</f>
         <v/>
       </c>
       <c r="N58" s="62" t="n"/>
-      <c r="O58" s="59" t="n"/>
+      <c r="O58" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: accept_offer() tự mở hội thoại ngay khi ghép xong; Celery beat close-stale-chat chạy mỗi giờ đóng hội thoại của chuyến đã kết thúc quá 24h. Không có thao tác tay nào.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="22.35" customHeight="1" s="38">
       <c r="A59" s="62" t="inlineStr">
@@ -6236,11 +6256,11 @@
       </c>
       <c r="K62" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L62" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="63">
         <f>H62*(1-L62)</f>
@@ -6249,7 +6269,7 @@
       <c r="N62" s="62" t="n"/>
       <c r="O62" s="59" t="inlineStr">
         <is>
-          <t>Nối vào fraud_review_queue đã có sẵn</t>
+          <t>04/09 XONG: detect_off_app_payment() quét số tài khoản, tên ngân hàng, link ví, lời rủ chuyển khoản → gắn cờ để rà soát. CỐ Ý KHÔNG CHẶN TIN: chặn nhầm là hai bên chuyển sang Zalo và mất luôn dấu vết, tệ hơn nhiều so với một cờ báo nhầm. Tin hệ thống không bị quét.</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6444,11 @@
       </c>
       <c r="K65" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L65" s="64" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M65" s="63">
         <f>H65*(1-L65)</f>
@@ -6437,7 +6457,7 @@
       <c r="N65" s="62" t="n"/>
       <c r="O65" s="59" t="inlineStr">
         <is>
-          <t>connection_manager + Redis pub/sub đã có, cần mở rộng topic</t>
+          <t>04/09: một kết nối /ws đã phục vụ đủ chat.typing + location_update + trip_offer_response + ops.fleet_update, và có auth.expired khi token hết hạn giữa chừng (test bảo mật chứng minh). CÒN LẠI: cơ chế ack và hàng đợi gửi lại phía server — làm cùng P2-15 để client và server khớp giao thức.</t>
         </is>
       </c>
     </row>

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -6076,18 +6076,22 @@
       </c>
       <c r="K59" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L59" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="63">
         <f>H59*(1-L59)</f>
         <v/>
       </c>
       <c r="N59" s="62" t="n"/>
-      <c r="O59" s="59" t="n"/>
+      <c r="O59" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: domains/support đủ ticket + ticket_events + SLA + leo thang. Migration 0010 chạy sạch cả hai chiều trên PostgreSQL 16 thật. SLA đo PHẢN HỒI ĐẦU TIÊN (đo lúc đóng ticket thì mọi chỉ số đều đẹp và không nói gì cả); quá hạn thì beat mỗi phút tự đẩy sang escalated. Agent offline quá 10 phút thì ticket tự quay về hàng đợi. Mức ưu tiên do LOẠI vấn đề quyết định: khách đánh dấu một vụ tai nạn là 'thấp' vẫn thành urgent.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="22.35" customHeight="1" s="38">
       <c r="A60" s="62" t="inlineStr">
@@ -6136,18 +6140,22 @@
       </c>
       <c r="K60" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L60" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="63">
         <f>H60*(1-L60)</f>
         <v/>
       </c>
       <c r="N60" s="62" t="n"/>
-      <c r="O60" s="59" t="n"/>
+      <c r="O60" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: pick_agent() lọc theo đúng đội + còn slot + đang trực, rồi ưu tiên agent ĐÃ TỪNG xử lý ticket của chính khách này (kể lại từ đầu cho người mới là cách nhanh nhất làm khách tức giận thêm lần nữa). Cả đội kín thì ticket nằm hàng đợi chung ở trạng thái new, không gán bừa cho người đang bận.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="38">
       <c r="A61" s="62" t="inlineStr">
@@ -6196,18 +6204,22 @@
       </c>
       <c r="K61" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L61" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="63">
         <f>H61*(1-L61)</f>
         <v/>
       </c>
       <c r="N61" s="62" t="n"/>
-      <c r="O61" s="59" t="n"/>
+      <c r="O61" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: canned_responses theo đội + gõ tắt. /hoantien và hoantien đều ra mẫu; mẫu của đội khác không lẫn sang; mẫu tắt (is_active=false) không gọi ra được. Sửa mẫu đòi quyền support:conversation:read_all — một câu trả lời sai gửi cho hàng nghìn khách.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="22.35" customHeight="1" s="38">
       <c r="A62" s="62" t="inlineStr">
@@ -6628,18 +6640,22 @@
       </c>
       <c r="K68" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L68" s="64" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M68" s="63">
         <f>H68*(1-L68)</f>
         <v/>
       </c>
       <c r="N68" s="62" t="n"/>
-      <c r="O68" s="59" t="n"/>
+      <c r="O68" s="59" t="inlineStr">
+        <is>
+          <t>04/09: backend xong — POST /ops/chat/conversations/{id}/join và /leave, sinh tin hệ thống cho cả hai bên, rời đi ghi mốc left_at chứ không xoá dòng. CÒN LẠI: nút bấm trên Console.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="22.35" customHeight="1" s="38">
       <c r="A69" s="62" t="inlineStr">
@@ -6688,18 +6704,22 @@
       </c>
       <c r="K69" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="L69" s="64" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M69" s="63">
         <f>H69*(1-L69)</f>
         <v/>
       </c>
       <c r="N69" s="62" t="n"/>
-      <c r="O69" s="59" t="n"/>
+      <c r="O69" s="59" t="inlineStr">
+        <is>
+          <t>04/09: backend xong — GET /ops/chat/search (lọc theo khách/chuyến) và GET /ops/chat/conversations/{id}/messages, cả hai đòi support:conversation:read_all và đi qua audit log. CÒN LẠI: màn hình tra cứu trên Console (P2-16 nhóm UI).</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="38">
       <c r="A70" s="62" t="inlineStr">

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -6332,18 +6332,22 @@
       </c>
       <c r="K63" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L63" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="63">
         <f>H63*(1-L63)</f>
         <v/>
       </c>
       <c r="N63" s="62" t="n"/>
-      <c r="O63" s="59" t="n"/>
+      <c r="O63" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: POST /chat/attachments cấp URL tải lên ký hạn 15 phút, ảnh đi THẲNG lên kho chứ không qua backend (một ảnh 5MB đi qua API là chiếm một worker suốt thời gian truyền). Khoá lưu trữ do SERVER sinh — cho client đặt tên là cho phép ghi đè tệp của người khác bằng cách đoán tên. Chặn quá 5MB và sai định dạng NGAY lúc xin URL. URL đọc sinh mới mỗi lần xem, không lưu. Không gắn được ảnh của người khác / của hội thoại khác / gắn hai lần. Beat 4h sáng dọn tệp xin URL rồi bỏ ngang. LƯU Ý: quét virus vẫn là chỗ trống — cột scanned_at/scan_result đã có, cần nhà cung cấp thật.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="38">
       <c r="A64" s="62" t="inlineStr">
@@ -6392,11 +6396,11 @@
       </c>
       <c r="K64" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L64" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="63">
         <f>H64*(1-L64)</f>
@@ -6405,7 +6409,7 @@
       <c r="N64" s="62" t="n"/>
       <c r="O64" s="59" t="inlineStr">
         <is>
-          <t>notifications hiện chỉ đẩy WS, chưa có push thật</t>
+          <t>04/09 XONG: bảng push_tokens (một dòng cho mỗi TOKEN, không phải mỗi người) + integrations/push.py. Gửi tin xong đẩy việc vào Celery với countdown 5 giây; lúc chạy mới kiểm lại, còn chưa đọc thì mới push. Bắn ngay là gửi thông báo cho tin người ta vừa đọc xong — cách nhanh nhất để người dùng tắt thông báo của ứng dụng. NỘI DUNG TIN KHÔNG vào payload: thông báo hiện trên màn hình khoá. Token chết bị gỡ ngay sau lần gửi thất bại; token đổi chủ khi máy đó đăng nhập tài khoản khác.</t>
         </is>
       </c>
     </row>
@@ -6888,18 +6892,22 @@
       </c>
       <c r="K72" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L72" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="63">
         <f>H72*(1-L72)</f>
         <v/>
       </c>
       <c r="N72" s="62" t="n"/>
-      <c r="O72" s="59" t="n"/>
+      <c r="O72" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: beat 4h30 sáng ẩn danh hoá tin quá hạn — chat chuyến 12 tháng, chat hỗ trợ 24 tháng (bằng chứng khiếu nại, mà khiếu nại đến muộn). ẨN DANH HOÁ chứ không xoá dòng: xoá là mất luôn khả năng trả lời 'hai người này có từng nhắn tin cho nhau không' — câu hỏi mà cả toà án lẫn đội chống gian lận đều sẽ hỏi. Chạy lại không đếm lại dòng đã xử lý.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="38">
       <c r="A73" s="62" t="inlineStr">

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -6460,11 +6460,11 @@
       </c>
       <c r="K65" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L65" s="64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M65" s="63">
         <f>H65*(1-L65)</f>
@@ -6473,7 +6473,7 @@
       <c r="N65" s="62" t="n"/>
       <c r="O65" s="59" t="inlineStr">
         <is>
-          <t>04/09: một kết nối /ws đã phục vụ đủ chat.typing + location_update + trip_offer_response + ops.fleet_update, và có auth.expired khi token hết hạn giữa chừng (test bảo mật chứng minh). CÒN LẠI: cơ chế ack và hàng đợi gửi lại phía server — làm cùng P2-15 để client và server khớp giao thức.</t>
+          <t>04/09 XONG: một kết nối /ws phục vụ chat.typing + location_update + trip_offer_response + ops.fleet_update, có auth.expired khi token hết hạn giữa chừng. Cơ chế ack và hàng đợi gửi lại nay nằm ở packages/realtime-client (P2-15) — phía client giữ tin tới khi có ack, quá hạn thì gửi lại, dùng chung client_msg_id với khử trùng của backend nên gửi lại không tạo tin thứ hai.</t>
         </is>
       </c>
     </row>
@@ -6524,18 +6524,22 @@
       </c>
       <c r="K66" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L66" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="63">
         <f>H66*(1-L66)</f>
         <v/>
       </c>
       <c r="N66" s="62" t="n"/>
-      <c r="O66" s="59" t="n"/>
+      <c r="O66" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: packages/realtime-client — không phụ thuộc DOM ngoài WebSocket nên chạy được cả web lẫn React Native. Nối lại LÙI DẦN có nhiễu ngẫu nhiên (1s→30s): nối lại ngay mỗi giây là cách biến một sự cố ngắn của server thành sự cố dài, vì server vừa sống lại thì toàn bộ client đập vào cùng lúc. Gửi lúc đang đứt thì xếp hàng chứ không ném lỗi. URL là HÀM chứ không phải chuỗi — nối lại phải dùng token mới, không phải token đã chết. 15 test, trong đó test bắt được một lỗi thật: sau khi createSocket ném lỗi, client kẹt ở trạng thái 'connecting' và không bao giờ thử lại nữa.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="22.35" customHeight="1" s="38">
       <c r="A67" s="62" t="inlineStr">
@@ -6584,18 +6588,22 @@
       </c>
       <c r="K67" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L67" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="63">
         <f>H67*(1-L67)</f>
         <v/>
       </c>
       <c r="N67" s="62" t="n"/>
-      <c r="O67" s="59" t="n"/>
+      <c r="O67" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: màn hình Support Desk hai cột — hàng đợi (sắp theo hạn SLA, tự làm mới 15 giây, ticket quá hạn hiện đỏ) và khung xử lý (thông tin ticket + hội thoại + ô soạn). MỘT nút 'Gửi trả lời' gọi endpoint làm cả ba việc ở backend: vào hội thoại, gửi tin, đóng đồng hồ SLA — tách ra ba nút là mời agent quên hai nút cuối rồi báo cáo hiện 'chưa phản hồi' cho ticket đã trả lời. Gõ tắt /hoantien chèn mẫu ngay trong ô soạn.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="38">
       <c r="A68" s="62" t="inlineStr">
@@ -6644,11 +6652,11 @@
       </c>
       <c r="K68" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L68" s="64" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M68" s="63">
         <f>H68*(1-L68)</f>
@@ -6657,7 +6665,7 @@
       <c r="N68" s="62" t="n"/>
       <c r="O68" s="59" t="inlineStr">
         <is>
-          <t>04/09: backend xong — POST /ops/chat/conversations/{id}/join và /leave, sinh tin hệ thống cho cả hai bên, rời đi ghi mốc left_at chứ không xoá dòng. CÒN LẠI: nút bấm trên Console.</t>
+          <t>04/09 XONG: nút Tham gia chat / Rời chat ngay trong màn hình ticket, gọi /ops/chat/conversations/{id}/join|leave. Cả khách và tài xế đều thấy tin hệ thống; rời đi ghi mốc left_at chứ không xoá dòng.</t>
         </is>
       </c>
     </row>
@@ -6708,11 +6716,11 @@
       </c>
       <c r="K69" s="62" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L69" s="64" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M69" s="63">
         <f>H69*(1-L69)</f>
@@ -6721,7 +6729,7 @@
       <c r="N69" s="62" t="n"/>
       <c r="O69" s="59" t="inlineStr">
         <is>
-          <t>04/09: backend xong — GET /ops/chat/search (lọc theo khách/chuyến) và GET /ops/chat/conversations/{id}/messages, cả hai đòi support:conversation:read_all và đi qua audit log. CÒN LẠI: màn hình tra cứu trên Console (P2-16 nhóm UI).</t>
+          <t>04/09 XONG: màn hình Tra cứu lịch sử chat — lọc theo khách hoặc chuyến, mở đọc nội dung. Đòi quyền support:conversation:read_all (không phải read_own) và mỗi lần mở đều nằm trong nhật ký thao tác: tra cứu được mà không để lại dấu vết thì không còn là tra cứu, nó là đọc trộm. Giao diện nói thẳng điều đó với người xem.</t>
         </is>
       </c>
     </row>
@@ -6772,18 +6780,22 @@
       </c>
       <c r="K70" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L70" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="63">
         <f>H70*(1-L70)</f>
         <v/>
       </c>
       <c r="N70" s="62" t="n"/>
-      <c r="O70" s="59" t="n"/>
+      <c r="O70" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: GET /ops/support/stats + màn hình SLA CSKH. Bốn chỉ số §7.5: phản hồi đầu, thời gian xử lý, tỷ lệ reopen, tỷ lệ đạt SLA — theo tổng và theo từng agent. Quá hạn chưa phản hồi đếm trên ticket CÒN MỞ, không đợi tới lúc đóng. Chỉ số rỗng hiện là '—' chứ KHÔNG phải 0: 'chưa có số liệu' và 'phản hồi tức thì' là hai chuyện khác nhau, biến cái đầu thành 0 là nói dối bằng biểu đồ.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="38">
       <c r="A71" s="62" t="inlineStr">

--- a/docs/GoAn_Project_Tracker.xlsx
+++ b/docs/GoAn_Project_Tracker.xlsx
@@ -6844,18 +6844,22 @@
       </c>
       <c r="K71" s="62" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="L71" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="63">
         <f>H71*(1-L71)</f>
         <v/>
       </c>
       <c r="N71" s="62" t="n"/>
-      <c r="O71" s="59" t="n"/>
+      <c r="O71" s="59" t="inlineStr">
+        <is>
+          <t>04/09 XONG: beat 4h30 sáng ẩn danh hoá tin quá hạn — chat chuyến 12 tháng, chat hỗ trợ 24 tháng (bằng chứng khiếu nại, mà khiếu nại đến muộn). ẨN DANH HOÁ chứ không xoá dòng: xoá là mất luôn khả năng trả lời 'hai người này có từng nhắn tin cho nhau không' — câu hỏi mà cả toà án lẫn đội chống gian lận đều sẽ hỏi. Chạy lại không đếm lại dòng đã xử lý.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="22.35" customHeight="1" s="38">
       <c r="A72" s="62" t="inlineStr">
@@ -6917,7 +6921,7 @@
       <c r="N72" s="62" t="n"/>
       <c r="O72" s="59" t="inlineStr">
         <is>
-          <t>04/09 XONG: beat 4h30 sáng ẩn danh hoá tin quá hạn — chat chuyến 12 tháng, chat hỗ trợ 24 tháng (bằng chứng khiếu nại, mà khiếu nại đến muộn). ẨN DANH HOÁ chứ không xoá dòng: xoá là mất luôn khả năng trả lời 'hai người này có từng nhắn tin cho nhau không' — câu hỏi mà cả toà án lẫn đội chống gian lận đều sẽ hỏi. Chạy lại không đếm lại dòng đã xử lý.</t>
+          <t>04/09 XONG: tests/domains/test_chat_scenarios.py — 10 kịch bản trọn vòng đi qua đúng chuỗi middleware thật (mất mạng giữa chừng + gửi trùng, CSKH vào/ra 3 bên, gửi ảnh rồi tra cứu lại khi khiếu nại, push khi đóng app, vòng ticket từ mở tới reopen, hai thiết bị đọc lệch, hội thoại đóng sau 24h, cờ ngoài app, thu quyền khi rời hội thoại, tin hệ thống). Mỗi bài kết thúc bằng phép đếm 'không mất tin, không trùng tin'. Kèm 11 bước mới trong make smoke (33/33 trên Postgres thật). BẮT ĐƯỢC LỖI THẬT: gửi lại ảnh sau khi mất sóng bị trả 409 vì router gắn ảnh TRƯỚC khi khử trùng tin — đúng lúc người dùng đang cố gửi ảnh hiện trường tai nạn. Đã sửa và có test hồi quy riêng.</t>
         </is>
       </c>
     </row>
@@ -6979,11 +6983,7 @@
         <v/>
       </c>
       <c r="N73" s="62" t="n"/>
-      <c r="O73" s="59" t="inlineStr">
-        <is>
-          <t>Chưa có app tài xế — đây là phần rủi ro kỹ thuật cao nhất dự án</t>
-        </is>
-      </c>
+      <c r="O73" s="59" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" s="38">
       <c r="A74" s="62" t="inlineStr">
